--- a/docs/balance/balance-realistic.xlsx
+++ b/docs/balance/balance-realistic.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Balance del modo Realistic — generado automáticamente con el motor vigente</t>
   </si>
@@ -29,6 +29,9 @@
     <t>Referencia con desgaste medio (25 %) — cada 10 horas de vuelo</t>
   </si>
   <si>
+    <t>Experiencia por vuelo (3 h; desgaste 0 / 25 / 100 %)</t>
+  </si>
+  <si>
     <t>Perfil</t>
   </si>
   <si>
@@ -44,9 +47,30 @@
     <t>Total</t>
   </si>
   <si>
+    <t>Desgaste</t>
+  </si>
+  <si>
+    <t>E[fallas]</t>
+  </si>
+  <si>
+    <t>P(≥1 falla)</t>
+  </si>
+  <si>
+    <t>P(≥1 grave)</t>
+  </si>
+  <si>
+    <t>P(≥1 crítica)</t>
+  </si>
+  <si>
+    <t>1 crítica cada</t>
+  </si>
+  <si>
     <t>Bajo</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>Moderado</t>
   </si>
   <si>
@@ -74,28 +98,7 @@
     <t>1 crítica cada… (25 %)</t>
   </si>
   <si>
-    <t>Experiencia por vuelo (1,5 h, desgaste 25 %)</t>
-  </si>
-  <si>
-    <t>E[fallas]</t>
-  </si>
-  <si>
-    <t>P(≥1 falla)</t>
-  </si>
-  <si>
-    <t>P(≥1 grave)</t>
-  </si>
-  <si>
-    <t>P(≥1 crítica)</t>
-  </si>
-  <si>
-    <t>1 crítica cada</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>Ancla temporal del desgaste (vuelos de 1,5 h hasta cada nivel; el seed va de 0,1 a 0,6 %/h)</t>
+    <t>Ancla temporal del desgaste (vuelos de 3 h; el seed va de 0,1 a 0,6 %/h)</t>
   </si>
   <si>
     <t>Tasa del sistema</t>
@@ -128,42 +131,48 @@
     <t>Cada 1 h de vuelo</t>
   </si>
   <si>
-    <t>Desgaste</t>
+    <t>Semilla de tierra (fallas esperadas al iniciar cada vuelo)</t>
+  </si>
+  <si>
+    <t>Fallas al inicio</t>
   </si>
   <si>
     <t>Cada 10 h de vuelo</t>
   </si>
   <si>
+    <t>Experiencia por vuelo (3 h)</t>
+  </si>
+  <si>
     <t>Cada 100 h de vuelo</t>
   </si>
   <si>
-    <t>Semilla de tierra (fallas esperadas al iniciar cada vuelo)</t>
-  </si>
-  <si>
-    <t>Fallas al inicio</t>
+    <t>Datos de la gráfica: E[fallas por vuelo de 3 h] por severidad</t>
   </si>
   <si>
     <t>Perfil Moderado (nivel 2)</t>
   </si>
   <si>
-    <t>Multiplicador ×1 · desgaste máx ×3 · tope agravación 5 · tope tierra 2 · tregua crítica 120 min</t>
+    <t>Multiplicador ×1 · desgaste máx ×2,5 · tope agravación 5 · tope tierra 2 · tregua crítica 120 min</t>
   </si>
   <si>
     <t>Perfil Alto (nivel 3)</t>
   </si>
   <si>
-    <t>Multiplicador ×1,5 · desgaste máx ×4 · tope agravación 8 · tope tierra 3 · tregua crítica 60 min</t>
+    <t>Multiplicador ×2,5 · desgaste máx ×3 · tope agravación 8 · tope tierra 3 · tregua crítica 60 min</t>
   </si>
   <si>
     <t>Perfil 7700 (nivel 4)</t>
   </si>
   <si>
-    <t>Multiplicador ×2,5 · desgaste máx ×5,5 · tope agravación 10 · tope tierra 5 · tregua crítica 30 min</t>
+    <t>Multiplicador ×5 · desgaste máx ×4 · tope agravación 10 · tope tierra 5 · tregua crítica 30 min</t>
   </si>
   <si>
     <t>Tendencias del balance</t>
   </si>
   <si>
+    <t>Datos: E[fallas por vuelo de 3 h] según desgaste (fuente de la gráfica de experiencia)</t>
+  </si>
+  <si>
     <t>Configuración del código con la que se generó este reporte</t>
   </si>
   <si>
@@ -173,24 +182,51 @@
     <t>Física del motor (Physics)</t>
   </si>
   <si>
+    <t>Perfiles vigentes (defaults de código)</t>
+  </si>
+  <si>
     <t>Parámetro</t>
   </si>
   <si>
     <t>Valor</t>
   </si>
   <si>
+    <t>Multiplicador</t>
+  </si>
+  <si>
+    <t>Desgaste máx</t>
+  </si>
+  <si>
+    <t>Tope agravación</t>
+  </si>
+  <si>
+    <t>Tope tierra</t>
+  </si>
+  <si>
+    <t>Tregua crítica</t>
+  </si>
+  <si>
     <t>Tasa base por falla leve elegible en vuelo, eventos/h (FailureRatePerHourBase)</t>
   </si>
   <si>
     <t>Probabilidad base por falla leve en la semilla de tierra (GroundSeedBaseProbability)</t>
   </si>
   <si>
+    <t>120 min</t>
+  </si>
+  <si>
     <t>Multiplicador de tasa: leves (SeverityRateMultiplier.Minor)</t>
   </si>
   <si>
+    <t>60 min</t>
+  </si>
+  <si>
     <t>Multiplicador de tasa: graves (SeverityRateMultiplier.Major)</t>
   </si>
   <si>
+    <t>30 min</t>
+  </si>
+  <si>
     <t>Multiplicador de tasa: críticas (SeverityRateMultiplier.Critical)</t>
   </si>
   <si>
@@ -240,33 +276,6 @@
   </si>
   <si>
     <t>Ventana posterior al arribo, h (PostArrivalWindowHours)</t>
-  </si>
-  <si>
-    <t>Perfiles vigentes (defaults de código)</t>
-  </si>
-  <si>
-    <t>Multiplicador</t>
-  </si>
-  <si>
-    <t>Desgaste máx</t>
-  </si>
-  <si>
-    <t>Tope agravación</t>
-  </si>
-  <si>
-    <t>Tope tierra</t>
-  </si>
-  <si>
-    <t>Tregua crítica</t>
-  </si>
-  <si>
-    <t>120 min</t>
-  </si>
-  <si>
-    <t>60 min</t>
-  </si>
-  <si>
-    <t>30 min</t>
   </si>
 </sst>
 </file>
@@ -275,9 +284,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0 %"/>
-    <numFmt numFmtId="165" formatCode="0.0 &quot;h&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0 &quot; %&quot;"/>
-    <numFmt numFmtId="167" formatCode="0 &quot;vuelos&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0 &quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="0 &quot;vuelos&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0 &quot;h&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
@@ -378,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" xfId="0" applyProtection="1"/>
@@ -391,19 +400,26 @@
     <xf numFmtId="2" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="2" applyNumberFormat="1" fontId="6" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="2" applyNumberFormat="1" fontId="6" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="165" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="165" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="166" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="166" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="6" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="166" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="167" applyNumberFormat="1" fontId="6" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="167" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="1" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
     <xf numFmtId="168" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
@@ -415,6 +431,654 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Perfil Bajo: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Leves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Bajo'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Bajo'!$J$22:$J$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Graves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Bajo'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Bajo'!$K$22:$K$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Críticas</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Bajo'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Bajo'!$L$22:$L$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Perfil Moderado: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Leves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Moderado'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Moderado'!$J$22:$J$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Graves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Moderado'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Moderado'!$K$22:$K$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Críticas</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Moderado'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Moderado'!$L$22:$L$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Perfil Alto: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Leves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Alto'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Alto'!$J$22:$J$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Graves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Alto'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Alto'!$K$22:$K$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Críticas</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Alto'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Alto'!$L$22:$L$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Perfil 7700: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Leves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$J$22:$J$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Graves</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$K$22:$K$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Críticas</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$I$22:$I$26</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$L$22:$L$26</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:chart>
     <c:title>
@@ -605,7 +1269,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:chart>
     <c:title>
@@ -796,7 +1460,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:chart>
     <c:title>
@@ -893,6 +1557,337 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr/>
+              <a:t>Experiencia por vuelo: fallas esperadas en 3 h, según desgaste</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Bajo</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Gráficas'!$A$49:$A$53</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gráficas'!$B$49:$B$53</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Moderado</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Gráficas'!$A$49:$A$53</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gráficas'!$C$49:$C$53</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="F59E0B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Alto</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Gráficas'!$A$49:$A$53</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gráficas'!$D$49:$D$53</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="EF4444"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>7700</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="square"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Gráficas'!$A$49:$A$53</c:f>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Gráficas'!$E$49:$E$53</c:f>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="8B5CF6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+        </ser>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1"/>
+        <c:axId val="2"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Experiencia_Bajo"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Experiencia_Moderado"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Experiencia_Alto"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Experiencia_7700"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -910,7 +1905,7 @@
     </xdr:to>
     <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="GravesPorDesgaste"/>
+        <xdr:cNvPr id="4" name="GravesPorDesgaste"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -927,20 +1922,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>3619500</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="CriticasPorDesgaste"/>
+        <xdr:cNvPr id="5" name="CriticasPorDesgaste"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -959,18 +1954,18 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>7239000</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="GravesPorPerfil"/>
+        <xdr:cNvPr id="6" name="GravesPorPerfil"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -985,20 +1980,57 @@
     </graphicFrame>
     <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="ExperienciaPorDesgaste"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="81.76423645019531" customWidth="1"/>
+    <col min="1" max="1" width="65.23560333251953" customWidth="1"/>
     <col min="2" max="2" width="13.4940767288208" customWidth="1"/>
     <col min="3" max="3" width="12.09656810760498" customWidth="1"/>
     <col min="4" max="4" width="17.720359802246094" customWidth="1"/>
     <col min="5" max="5" width="13.865448951721191" customWidth="1"/>
     <col min="6" max="6" width="20.73737907409668" customWidth="1"/>
+    <col min="9" max="9" width="47.221466064453125" customWidth="1"/>
+    <col min="10" max="10" width="9.505144119262695" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.0315580368042" customWidth="1"/>
+    <col min="13" max="13" width="11.525697708129883" customWidth="1"/>
+    <col min="14" max="14" width="12.009608268737793" customWidth="1"/>
+    <col min="15" max="15" width="13.120657920837402" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,27 +2047,51 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="s">
-        <v>8</v>
+      <c r="A6" s="22" t="s">
+        <v>15</v>
       </c>
       <c r="B6" s="8">
         <v>1.7999999999999998</v>
@@ -1049,86 +2105,258 @@
       <c r="E6" s="8">
         <v>2.4</v>
       </c>
+      <c r="I6" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="L6" s="13">
+        <v>43.78575548031775</v>
+      </c>
+      <c r="M6" s="13">
+        <v>13.4112251940795</v>
+      </c>
+      <c r="N6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="8">
+        <v>3.3000000000000003</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="E7" s="8">
+        <v>4.73</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="L7" s="14">
+        <v>51.324774404002824</v>
+      </c>
+      <c r="M7" s="14">
+        <v>16.4729788588728</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="8">
         <v>9</v>
       </c>
-      <c r="B7" s="8">
-        <v>3.6000000000000005</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="E7" s="8">
-        <v>5.160000000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="s">
+      <c r="C8" s="8">
+        <v>3.0000000000000004</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="E8" s="8">
+        <v>12.9</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="L8" s="13">
+        <v>68.39958713081376</v>
+      </c>
+      <c r="M8" s="13">
+        <v>25.023840776095874</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="8">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="D9" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>30.1</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1.032</v>
+      </c>
+      <c r="L9" s="13">
+        <v>64.37063398138412</v>
+      </c>
+      <c r="M9" s="13">
+        <v>21.337213893344664</v>
+      </c>
+      <c r="N9" s="13">
+        <v>6.946910418879426</v>
+      </c>
+      <c r="O9" s="18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="I10" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1.4190000000000003</v>
+      </c>
+      <c r="L10" s="14">
+        <v>75.80441481887624</v>
+      </c>
+      <c r="M10" s="14">
+        <v>28.107626656807383</v>
+      </c>
+      <c r="N10" s="14">
+        <v>9.42572919764515</v>
+      </c>
+      <c r="O10" s="19">
         <v>10</v>
       </c>
-      <c r="B8" s="8">
-        <v>6.300000000000001</v>
-      </c>
-      <c r="C8" s="8">
-        <v>2.1000000000000005</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.6300000000000001</v>
-      </c>
-      <c r="E8" s="8">
-        <v>9.030000000000003</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="8">
-        <v>12.75</v>
-      </c>
-      <c r="C9" s="8">
-        <v>4.25</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.275</v>
-      </c>
-      <c r="E9" s="8">
-        <v>18.275</v>
+    </row>
+    <row r="11">
+      <c r="I11" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>2.58</v>
+      </c>
+      <c r="L11" s="13">
+        <v>92.42259959771545</v>
+      </c>
+      <c r="M11" s="13">
+        <v>45.11883639059736</v>
+      </c>
+      <c r="N11" s="13">
+        <v>16.4729788588728</v>
+      </c>
+      <c r="O11" s="18">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>2.58</v>
+      </c>
+      <c r="L12" s="13">
+        <v>92.42259959771545</v>
+      </c>
+      <c r="M12" s="13">
+        <v>45.11883639059736</v>
+      </c>
+      <c r="N12" s="13">
+        <v>16.4729788588728</v>
+      </c>
+      <c r="O12" s="18">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="A13" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="K13" s="9">
+        <v>3.87</v>
+      </c>
+      <c r="L13" s="14">
+        <v>97.91416305747853</v>
+      </c>
+      <c r="M13" s="14">
+        <v>59.3430340259401</v>
+      </c>
+      <c r="N13" s="14">
+        <v>23.662050566314687</v>
+      </c>
+      <c r="O13" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="s">
         <v>15</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="s">
-        <v>8</v>
       </c>
       <c r="B14" s="8">
         <v>0.72</v>
@@ -1142,240 +2370,219 @@
       <c r="E14" s="10">
         <v>0</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="26">
         <v>0</v>
       </c>
+      <c r="I14" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="6">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8">
+        <v>7.74</v>
+      </c>
+      <c r="L14" s="13">
+        <v>99.95649284249212</v>
+      </c>
+      <c r="M14" s="13">
+        <v>83.47011117784136</v>
+      </c>
+      <c r="N14" s="13">
+        <v>41.725174762601036</v>
+      </c>
+      <c r="O14" s="18">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
-        <v>9</v>
+      <c r="A15" s="23" t="s">
+        <v>17</v>
       </c>
       <c r="B15" s="8">
-        <v>1.6</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="C15" s="8">
         <v>0.8000000000000002</v>
       </c>
       <c r="D15" s="8">
-        <v>2.4000000000000004</v>
+        <v>2</v>
       </c>
       <c r="E15" s="8">
-        <v>0.4800000000000001</v>
-      </c>
-      <c r="F15" s="21">
-        <v>27.8</v>
+        <v>0.42000000000000004</v>
+      </c>
+      <c r="F15" s="27">
+        <v>30.3</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>5.16</v>
+      </c>
+      <c r="L15" s="13">
+        <v>99.42583003143459</v>
+      </c>
+      <c r="M15" s="13">
+        <v>69.8805788087798</v>
+      </c>
+      <c r="N15" s="13">
+        <v>30.232367392896897</v>
+      </c>
+      <c r="O15" s="18">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="8">
+        <v>4</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8">
+        <v>6.000000000000001</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="F16" s="27">
+        <v>11.1</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="K16" s="9">
+        <v>9.030000000000001</v>
+      </c>
+      <c r="L16" s="14">
+        <v>99.9880237506828</v>
+      </c>
+      <c r="M16" s="14">
+        <v>87.75435717470181</v>
+      </c>
+      <c r="N16" s="14">
+        <v>46.74081989931028</v>
+      </c>
+      <c r="O16" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="8">
         <v>10</v>
       </c>
-      <c r="B16" s="8">
-        <v>3.0000000000000004</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="D16" s="8">
-        <v>4.800000000000001</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="F16" s="21">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="8">
-        <v>6.5</v>
-      </c>
       <c r="C17" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="8">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E17" s="8">
-        <v>1.95</v>
-      </c>
-      <c r="F17" s="21">
-        <v>7.8</v>
+        <v>3</v>
+      </c>
+      <c r="F17" s="27">
+        <v>4.8</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>20.64</v>
+      </c>
+      <c r="L17" s="13">
+        <v>99.99999989131693</v>
+      </c>
+      <c r="M17" s="13">
+        <v>99.17702529509799</v>
+      </c>
+      <c r="N17" s="13">
+        <v>76.30722413178782</v>
+      </c>
+      <c r="O17" s="18">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>23</v>
+      <c r="A21" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="C22" s="22">
-        <v>30.232367392896897</v>
-      </c>
-      <c r="D22" s="22">
-        <v>8.60688147287718</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>24</v>
+      <c r="A22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="32">
+        <v>84</v>
+      </c>
+      <c r="C22" s="32">
+        <v>167</v>
+      </c>
+      <c r="D22" s="32">
+        <v>267</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="8">
-        <v>0.7740000000000002</v>
-      </c>
-      <c r="C23" s="22">
-        <v>53.88352847913417</v>
-      </c>
-      <c r="D23" s="22">
-        <v>16.4729788588728</v>
-      </c>
-      <c r="E23" s="22">
-        <v>5.256789349820168</v>
-      </c>
-      <c r="F23" s="24">
-        <v>19</v>
+      <c r="A23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="32">
+        <v>28</v>
+      </c>
+      <c r="C23" s="32">
+        <v>56</v>
+      </c>
+      <c r="D23" s="32">
+        <v>89</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="8">
-        <v>1.3545000000000003</v>
-      </c>
-      <c r="C24" s="22">
-        <v>74.19236996521622</v>
-      </c>
-      <c r="D24" s="22">
-        <v>27.02111257309433</v>
-      </c>
-      <c r="E24" s="22">
-        <v>9.017226537397004</v>
-      </c>
-      <c r="F24" s="24">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="8">
-        <v>2.74125</v>
-      </c>
-      <c r="C25" s="22">
-        <v>93.55103156158768</v>
-      </c>
-      <c r="D25" s="22">
-        <v>47.138769573400275</v>
-      </c>
-      <c r="E25" s="22">
-        <v>17.407391918135183</v>
-      </c>
-      <c r="F25" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="15" t="s">
+      <c r="A24" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="32">
+        <v>14</v>
+      </c>
+      <c r="C24" s="32">
         <v>28</v>
       </c>
-      <c r="D29" s="15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="25">
-        <v>167</v>
-      </c>
-      <c r="C30" s="25">
-        <v>334</v>
-      </c>
-      <c r="D30" s="25">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="25">
-        <v>56</v>
-      </c>
-      <c r="C31" s="25">
-        <v>112</v>
-      </c>
-      <c r="D31" s="25">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="25">
-        <v>28</v>
-      </c>
-      <c r="C32" s="25">
-        <v>56</v>
-      </c>
-      <c r="D32" s="25">
-        <v>89</v>
+      <c r="D24" s="32">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <headerFooter/>
 </worksheet>
@@ -1383,46 +2590,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.45537567138672" customWidth="1"/>
-    <col min="2" max="2" width="13.83680248260498" customWidth="1"/>
+    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
+    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
+    <col min="11" max="11" width="10.435111045837402" customWidth="1"/>
+    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
+    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
+    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -1441,6 +2663,12 @@
       <c r="E6" s="8">
         <v>0.192</v>
       </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0.15424029807434747</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7">
@@ -1458,6 +2686,12 @@
       <c r="E7" s="9">
         <v>0.24</v>
       </c>
+      <c r="I7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0.18892925754788115</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6">
@@ -1475,6 +2709,12 @@
       <c r="E8" s="8">
         <v>0.288</v>
       </c>
+      <c r="I8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.22219544420944856</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6">
@@ -1492,6 +2732,12 @@
       <c r="E9" s="8">
         <v>0.336</v>
       </c>
+      <c r="I9" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.254097213296716</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6">
@@ -1509,27 +2755,54 @@
       <c r="E10" s="8">
         <v>0.384</v>
       </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.28469052659863137</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1548,6 +2821,24 @@
       <c r="E14" s="8">
         <v>1.92</v>
       </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="K14" s="13">
+        <v>43.78575548031775</v>
+      </c>
+      <c r="L14" s="13">
+        <v>13.4112251940795</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7">
@@ -1565,6 +2856,24 @@
       <c r="E15" s="9">
         <v>2.4</v>
       </c>
+      <c r="I15" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="K15" s="14">
+        <v>51.324774404002824</v>
+      </c>
+      <c r="L15" s="14">
+        <v>16.4729788588728</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" s="16" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6">
@@ -1582,6 +2891,24 @@
       <c r="E16" s="8">
         <v>2.88</v>
       </c>
+      <c r="I16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.8639999999999999</v>
+      </c>
+      <c r="K16" s="13">
+        <v>57.85271852240823</v>
+      </c>
+      <c r="L16" s="13">
+        <v>19.426469812652037</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6">
@@ -1599,6 +2926,24 @@
       <c r="E17" s="8">
         <v>3.3600000000000003</v>
       </c>
+      <c r="I17" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1.008</v>
+      </c>
+      <c r="K17" s="13">
+        <v>63.50518535455063</v>
+      </c>
+      <c r="L17" s="13">
+        <v>22.27552619310539</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6">
@@ -1616,26 +2961,59 @@
       <c r="E18" s="8">
         <v>3.84</v>
       </c>
+      <c r="I18" s="6">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="K18" s="13">
+        <v>68.39958713081376</v>
+      </c>
+      <c r="L18" s="13">
+        <v>25.023840776095874</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="K21" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="L21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1655,6 +3033,18 @@
       <c r="E22" s="8">
         <v>19.2</v>
       </c>
+      <c r="I22" s="6">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0.43199999999999994</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7">
@@ -1672,6 +3062,18 @@
       <c r="E23" s="9">
         <v>24</v>
       </c>
+      <c r="I23" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.54</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6">
@@ -1689,6 +3091,18 @@
       <c r="E24" s="8">
         <v>28.799999999999997</v>
       </c>
+      <c r="I24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.648</v>
+      </c>
+      <c r="K24" s="8">
+        <v>0.21599999999999997</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6">
@@ -1706,6 +3120,18 @@
       <c r="E25" s="8">
         <v>33.6</v>
       </c>
+      <c r="I25" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0.756</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0.252</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6">
@@ -1723,111 +3149,86 @@
       <c r="E26" s="8">
         <v>38.4</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6">
+      <c r="I26" s="6">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8">
+        <v>0.8639999999999999</v>
+      </c>
+      <c r="K26" s="8">
+        <v>0.28800000000000003</v>
+      </c>
+      <c r="L26" s="10">
         <v>0</v>
-      </c>
-      <c r="B30" s="8">
-        <v>0.15424029807434747</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0.18892925754788115</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="B32" s="8">
-        <v>0.22219544420944856</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="B33" s="8">
-        <v>0.254097213296716</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6">
-        <v>1</v>
-      </c>
-      <c r="B34" s="8">
-        <v>0.28469052659863137</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.45537567138672" customWidth="1"/>
-    <col min="2" max="2" width="13.83680248260498" customWidth="1"/>
+    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
+    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
+    <col min="11" max="11" width="10.435111045837402" customWidth="1"/>
+    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
+    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
+    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>35</v>
+      <c r="A4" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -1846,22 +3247,34 @@
       <c r="E6" s="8">
         <v>0.34400000000000003</v>
       </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0.2760390792579295</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7">
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>0.36000000000000004</v>
+        <v>0.33</v>
       </c>
       <c r="C7" s="9">
-        <v>0.12000000000000002</v>
+        <v>0.11000000000000001</v>
       </c>
       <c r="D7" s="9">
-        <v>0.036000000000000004</v>
+        <v>0.033</v>
       </c>
       <c r="E7" s="9">
-        <v>0.5160000000000001</v>
+        <v>0.4730000000000001</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0.3760884077067357</v>
       </c>
     </row>
     <row r="8">
@@ -1869,16 +3282,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>0.48</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="C8" s="8">
-        <v>0.16000000000000003</v>
+        <v>0.14</v>
       </c>
       <c r="D8" s="8">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="E8" s="8">
-        <v>0.6880000000000001</v>
+        <v>0.6020000000000001</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.473282045782378</v>
       </c>
     </row>
     <row r="9">
@@ -1886,16 +3305,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="C9" s="8">
-        <v>0.2</v>
+        <v>0.17000000000000004</v>
       </c>
       <c r="D9" s="8">
-        <v>0.06</v>
+        <v>0.051000000000000004</v>
       </c>
       <c r="E9" s="8">
-        <v>0.8600000000000001</v>
+        <v>0.7310000000000001</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.5671991056391092</v>
       </c>
     </row>
     <row r="10">
@@ -1903,38 +3328,65 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>0.7200000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="C10" s="8">
-        <v>0.24000000000000005</v>
+        <v>0.2</v>
       </c>
       <c r="D10" s="8">
-        <v>0.07200000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E10" s="8">
-        <v>1.0320000000000003</v>
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.6575305947099431</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="s">
-        <v>37</v>
+      <c r="A12" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1953,22 +3405,58 @@
       <c r="E14" s="8">
         <v>3.4400000000000004</v>
       </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1.032</v>
+      </c>
+      <c r="K14" s="13">
+        <v>64.37063398138412</v>
+      </c>
+      <c r="L14" s="13">
+        <v>21.337213893344664</v>
+      </c>
+      <c r="M14" s="13">
+        <v>6.946910418879426</v>
+      </c>
+      <c r="N14" s="18">
+        <v>14</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7">
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>3.6000000000000005</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="C15" s="9">
-        <v>1.2000000000000002</v>
+        <v>1.1</v>
       </c>
       <c r="D15" s="9">
-        <v>0.36000000000000004</v>
+        <v>0.33</v>
       </c>
       <c r="E15" s="9">
-        <v>5.160000000000001</v>
+        <v>4.73</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="9">
+        <v>1.4190000000000003</v>
+      </c>
+      <c r="K15" s="14">
+        <v>75.80441481887624</v>
+      </c>
+      <c r="L15" s="14">
+        <v>28.107626656807383</v>
+      </c>
+      <c r="M15" s="14">
+        <v>9.42572919764515</v>
+      </c>
+      <c r="N15" s="19">
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1976,16 +3464,34 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="C16" s="8">
-        <v>1.6000000000000003</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D16" s="8">
-        <v>0.48</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="E16" s="8">
-        <v>6.880000000000001</v>
+        <v>6.020000000000001</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.8060000000000003</v>
+      </c>
+      <c r="K16" s="13">
+        <v>83.56899356695996</v>
+      </c>
+      <c r="L16" s="13">
+        <v>34.29531801849433</v>
+      </c>
+      <c r="M16" s="13">
+        <v>11.838515321658393</v>
+      </c>
+      <c r="N16" s="18">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1993,16 +3499,34 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="C17" s="8">
-        <v>2</v>
+        <v>1.7000000000000004</v>
       </c>
       <c r="D17" s="8">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="E17" s="8">
-        <v>8.600000000000001</v>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J17" s="8">
+        <v>2.1930000000000005</v>
+      </c>
+      <c r="K17" s="13">
+        <v>88.84184985064023</v>
+      </c>
+      <c r="L17" s="13">
+        <v>39.95044211877341</v>
+      </c>
+      <c r="M17" s="13">
+        <v>14.18702781886062</v>
+      </c>
+      <c r="N17" s="18">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -2010,37 +3534,70 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>7.200000000000001</v>
+        <v>6</v>
       </c>
       <c r="C18" s="8">
-        <v>2.4000000000000004</v>
+        <v>2</v>
       </c>
       <c r="D18" s="8">
-        <v>0.7200000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="E18" s="8">
-        <v>10.320000000000002</v>
+        <v>8.600000000000001</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>2.58</v>
+      </c>
+      <c r="K18" s="13">
+        <v>92.42259959771545</v>
+      </c>
+      <c r="L18" s="13">
+        <v>45.11883639059736</v>
+      </c>
+      <c r="M18" s="13">
+        <v>16.4729788588728</v>
+      </c>
+      <c r="N18" s="18">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="s">
-        <v>38</v>
+      <c r="A20" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="K21" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="L21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2060,22 +3617,46 @@
       <c r="E22" s="8">
         <v>34.400000000000006</v>
       </c>
+      <c r="I22" s="6">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0.24000000000000005</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.07200000000000001</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7">
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>36.00000000000001</v>
+        <v>33</v>
       </c>
       <c r="C23" s="9">
-        <v>12.000000000000002</v>
+        <v>11.000000000000002</v>
       </c>
       <c r="D23" s="9">
-        <v>3.6000000000000005</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="E23" s="9">
-        <v>51.600000000000016</v>
+        <v>47.30000000000001</v>
+      </c>
+      <c r="I23" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.99</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0.33000000000000007</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0.099</v>
       </c>
     </row>
     <row r="24">
@@ -2083,16 +3664,28 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>48</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="C24" s="8">
-        <v>16.000000000000004</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="D24" s="8">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="E24" s="8">
-        <v>68.80000000000001</v>
+        <v>60.20000000000001</v>
+      </c>
+      <c r="I24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="8">
+        <v>1.2600000000000002</v>
+      </c>
+      <c r="K24" s="8">
+        <v>0.42000000000000004</v>
+      </c>
+      <c r="L24" s="8">
+        <v>0.126</v>
       </c>
     </row>
     <row r="25">
@@ -2100,16 +3693,28 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C25" s="8">
-        <v>20</v>
+        <v>17.000000000000004</v>
       </c>
       <c r="D25" s="8">
-        <v>6</v>
+        <v>5.1000000000000005</v>
       </c>
       <c r="E25" s="8">
-        <v>86.00000000000001</v>
+        <v>73.10000000000001</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0.5100000000000001</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0.15300000000000002</v>
       </c>
     </row>
     <row r="26">
@@ -2117,122 +3722,97 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>72.00000000000001</v>
+        <v>60</v>
       </c>
       <c r="C26" s="8">
-        <v>24.000000000000004</v>
+        <v>20</v>
       </c>
       <c r="D26" s="8">
-        <v>7.200000000000001</v>
+        <v>6</v>
       </c>
       <c r="E26" s="8">
-        <v>103.20000000000003</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6">
-        <v>0</v>
-      </c>
-      <c r="B30" s="8">
-        <v>0.2760390792579295</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0.4088268896854821</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="B32" s="8">
-        <v>0.5362786494528111</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="B33" s="8">
-        <v>0.6575305947099431</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6">
+        <v>86.00000000000001</v>
+      </c>
+      <c r="I26" s="6">
         <v>1</v>
       </c>
-      <c r="B34" s="8">
-        <v>0.7720346355556913</v>
+      <c r="J26" s="8">
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="K26" s="8">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.45537567138672" customWidth="1"/>
-    <col min="2" max="2" width="13.83680248260498" customWidth="1"/>
+    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
+    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
+    <col min="11" max="11" width="10.435111045837402" customWidth="1"/>
+    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
+    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
+    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="s">
-        <v>35</v>
+      <c r="A4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -2240,16 +3820,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="8">
-        <v>0.36000000000000004</v>
+        <v>0.6</v>
       </c>
       <c r="C6" s="8">
-        <v>0.12000000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="D6" s="8">
-        <v>0.036000000000000004</v>
+        <v>0.06</v>
       </c>
       <c r="E6" s="8">
-        <v>0.5160000000000001</v>
+        <v>0.8600000000000001</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0.6914293040316685</v>
       </c>
     </row>
     <row r="7">
@@ -2257,16 +3843,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>0.6300000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C7" s="9">
-        <v>0.21000000000000008</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="D7" s="9">
-        <v>0.06300000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E7" s="9">
-        <v>0.9030000000000002</v>
+        <v>1.29</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1.0196826013476679</v>
       </c>
     </row>
     <row r="8">
@@ -2274,16 +3866,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>0.9000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C8" s="8">
-        <v>0.30000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="D8" s="8">
-        <v>0.09000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E8" s="8">
-        <v>1.2900000000000003</v>
+        <v>1.7200000000000002</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1.3247366613101321</v>
       </c>
     </row>
     <row r="9">
@@ -2291,16 +3889,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>1.1700000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="C9" s="8">
-        <v>0.39000000000000007</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="8">
-        <v>0.117</v>
+        <v>0.15</v>
       </c>
       <c r="E9" s="8">
-        <v>1.6770000000000003</v>
+        <v>2.15</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1.6006548428410656</v>
       </c>
     </row>
     <row r="10">
@@ -2308,38 +3912,65 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>1.4400000000000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C10" s="8">
-        <v>0.4800000000000001</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="D10" s="8">
-        <v>0.14400000000000002</v>
+        <v>0.18</v>
       </c>
       <c r="E10" s="8">
-        <v>2.0640000000000005</v>
+        <v>2.58</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1.8443946434174783</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="s">
-        <v>37</v>
+      <c r="A12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -2347,16 +3978,34 @@
         <v>0</v>
       </c>
       <c r="B14" s="8">
-        <v>3.6000000000000005</v>
+        <v>6</v>
       </c>
       <c r="C14" s="8">
-        <v>1.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="D14" s="8">
-        <v>0.36000000000000004</v>
+        <v>0.6</v>
       </c>
       <c r="E14" s="8">
-        <v>5.160000000000001</v>
+        <v>8.600000000000001</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2.58</v>
+      </c>
+      <c r="K14" s="13">
+        <v>92.42259959771545</v>
+      </c>
+      <c r="L14" s="13">
+        <v>45.11883639059736</v>
+      </c>
+      <c r="M14" s="13">
+        <v>16.4729788588728</v>
+      </c>
+      <c r="N14" s="18">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -2364,16 +4013,34 @@
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>6.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="C15" s="9">
-        <v>2.1000000000000005</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="D15" s="9">
-        <v>0.6300000000000001</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E15" s="9">
-        <v>9.030000000000003</v>
+        <v>12.9</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="9">
+        <v>3.87</v>
+      </c>
+      <c r="K15" s="14">
+        <v>97.91416305747853</v>
+      </c>
+      <c r="L15" s="14">
+        <v>59.3430340259401</v>
+      </c>
+      <c r="M15" s="14">
+        <v>23.662050566314687</v>
+      </c>
+      <c r="N15" s="19">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2381,16 +4048,34 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>9.000000000000002</v>
+        <v>12</v>
       </c>
       <c r="C16" s="8">
-        <v>3.0000000000000004</v>
+        <v>4</v>
       </c>
       <c r="D16" s="8">
-        <v>0.9000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="E16" s="8">
-        <v>12.900000000000002</v>
+        <v>17.200000000000003</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="8">
+        <v>5.16</v>
+      </c>
+      <c r="K16" s="13">
+        <v>99.42583003143459</v>
+      </c>
+      <c r="L16" s="13">
+        <v>69.8805788087798</v>
+      </c>
+      <c r="M16" s="13">
+        <v>30.232367392896897</v>
+      </c>
+      <c r="N16" s="18">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -2398,16 +4083,34 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>11.700000000000001</v>
+        <v>15</v>
       </c>
       <c r="C17" s="8">
-        <v>3.900000000000001</v>
+        <v>5</v>
       </c>
       <c r="D17" s="8">
-        <v>1.1700000000000002</v>
+        <v>1.5</v>
       </c>
       <c r="E17" s="8">
-        <v>16.770000000000003</v>
+        <v>21.5</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J17" s="8">
+        <v>6.449999999999999</v>
+      </c>
+      <c r="K17" s="13">
+        <v>99.84194778312639</v>
+      </c>
+      <c r="L17" s="13">
+        <v>77.68698398515703</v>
+      </c>
+      <c r="M17" s="13">
+        <v>36.23718483782267</v>
+      </c>
+      <c r="N17" s="18">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -2415,37 +4118,70 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>14.400000000000002</v>
+        <v>18</v>
       </c>
       <c r="C18" s="8">
-        <v>4.800000000000001</v>
+        <v>6.000000000000001</v>
       </c>
       <c r="D18" s="8">
-        <v>1.4400000000000002</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="E18" s="8">
-        <v>20.640000000000004</v>
+        <v>25.8</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>7.74</v>
+      </c>
+      <c r="K18" s="13">
+        <v>99.95649284249212</v>
+      </c>
+      <c r="L18" s="13">
+        <v>83.47011117784136</v>
+      </c>
+      <c r="M18" s="13">
+        <v>41.725174762601036</v>
+      </c>
+      <c r="N18" s="18">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="s">
-        <v>38</v>
+      <c r="A20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="K21" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="L21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2454,16 +4190,28 @@
         <v>0</v>
       </c>
       <c r="B22" s="8">
-        <v>36.00000000000001</v>
+        <v>60</v>
       </c>
       <c r="C22" s="8">
-        <v>12.000000000000002</v>
+        <v>20</v>
       </c>
       <c r="D22" s="8">
-        <v>3.6000000000000005</v>
+        <v>6</v>
       </c>
       <c r="E22" s="8">
-        <v>51.600000000000016</v>
+        <v>86.00000000000001</v>
+      </c>
+      <c r="I22" s="6">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1.7999999999999998</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.18</v>
       </c>
     </row>
     <row r="23">
@@ -2471,16 +4219,28 @@
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>63.000000000000014</v>
+        <v>89.99999999999999</v>
       </c>
       <c r="C23" s="9">
-        <v>21.000000000000007</v>
+        <v>30.000000000000004</v>
       </c>
       <c r="D23" s="9">
-        <v>6.300000000000002</v>
+        <v>9</v>
       </c>
       <c r="E23" s="9">
-        <v>90.30000000000003</v>
+        <v>129</v>
+      </c>
+      <c r="I23" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J23" s="8">
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="24">
@@ -2488,16 +4248,28 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>90.00000000000001</v>
+        <v>120</v>
       </c>
       <c r="C24" s="8">
-        <v>30.000000000000004</v>
+        <v>40</v>
       </c>
       <c r="D24" s="8">
-        <v>9.000000000000002</v>
+        <v>12</v>
       </c>
       <c r="E24" s="8">
-        <v>129.00000000000003</v>
+        <v>172.00000000000003</v>
+      </c>
+      <c r="I24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="8">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="K24" s="8">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="L24" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="25">
@@ -2505,16 +4277,28 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>117.00000000000001</v>
+        <v>150</v>
       </c>
       <c r="C25" s="8">
-        <v>39.00000000000001</v>
+        <v>50</v>
       </c>
       <c r="D25" s="8">
-        <v>11.700000000000001</v>
+        <v>15</v>
       </c>
       <c r="E25" s="8">
-        <v>167.70000000000002</v>
+        <v>215</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J25" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="K25" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="26">
@@ -2522,122 +4306,97 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>144.00000000000003</v>
+        <v>179.99999999999997</v>
       </c>
       <c r="C26" s="8">
-        <v>48.00000000000001</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="D26" s="8">
-        <v>14.400000000000002</v>
+        <v>18</v>
       </c>
       <c r="E26" s="8">
-        <v>206.40000000000006</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6">
-        <v>0</v>
-      </c>
-      <c r="B30" s="8">
-        <v>0.4177994911237905</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0.7250708238283152</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="B32" s="8">
-        <v>1.0196826013476679</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="B33" s="8">
-        <v>1.295467712923665</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6">
+        <v>258</v>
+      </c>
+      <c r="I26" s="6">
         <v>1</v>
       </c>
-      <c r="B34" s="8">
-        <v>1.5479875610319356</v>
+      <c r="J26" s="8">
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="K26" s="8">
+        <v>1.8000000000000003</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.45537567138672" customWidth="1"/>
-    <col min="2" max="2" width="13.83680248260498" customWidth="1"/>
+    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="9.140625" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
+    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
+    <col min="11" max="11" width="11.0315580368042" customWidth="1"/>
+    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
+    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
+    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="s">
-        <v>35</v>
+      <c r="A4" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -2645,16 +4404,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="8">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="C6" s="8">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D6" s="8">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E6" s="8">
-        <v>0.8600000000000001</v>
+        <v>1.7200000000000002</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1.39210782937486</v>
       </c>
     </row>
     <row r="7">
@@ -2662,16 +4427,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>1.275</v>
+        <v>2.1</v>
       </c>
       <c r="C7" s="9">
-        <v>0.42500000000000004</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="D7" s="9">
-        <v>0.1275</v>
+        <v>0.21</v>
       </c>
       <c r="E7" s="9">
-        <v>1.8275</v>
+        <v>3.0100000000000002</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="8">
+        <v>2.387038545299486</v>
       </c>
     </row>
     <row r="8">
@@ -2679,16 +4450,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="C8" s="8">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="D8" s="8">
-        <v>0.195</v>
+        <v>0.3</v>
       </c>
       <c r="E8" s="8">
-        <v>2.795</v>
+        <v>4.3</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="8">
+        <v>3.2437256854769796</v>
       </c>
     </row>
     <row r="9">
@@ -2696,16 +4473,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>2.625</v>
+        <v>3.9</v>
       </c>
       <c r="C9" s="8">
-        <v>0.875</v>
+        <v>1.3</v>
       </c>
       <c r="D9" s="8">
-        <v>0.2625</v>
+        <v>0.39</v>
       </c>
       <c r="E9" s="8">
-        <v>3.7625</v>
+        <v>5.59</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J9" s="8">
+        <v>3.8993720091628767</v>
       </c>
     </row>
     <row r="10">
@@ -2713,38 +4496,65 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="C10" s="8">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="D10" s="8">
-        <v>0.32999999999999996</v>
+        <v>0.48</v>
       </c>
       <c r="E10" s="8">
-        <v>4.73</v>
+        <v>6.880000000000001</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8">
+        <v>4.351241580084704</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>37</v>
+      <c r="A12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -2752,16 +4562,34 @@
         <v>0</v>
       </c>
       <c r="B14" s="8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="8">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E14" s="8">
-        <v>8.600000000000001</v>
+        <v>17.200000000000003</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8">
+        <v>5.16</v>
+      </c>
+      <c r="K14" s="13">
+        <v>99.42583003143459</v>
+      </c>
+      <c r="L14" s="13">
+        <v>69.8805788087798</v>
+      </c>
+      <c r="M14" s="13">
+        <v>30.232367392896897</v>
+      </c>
+      <c r="N14" s="18">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2769,16 +4597,34 @@
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>12.75</v>
+        <v>21</v>
       </c>
       <c r="C15" s="9">
-        <v>4.25</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="D15" s="9">
-        <v>1.275</v>
+        <v>2.1</v>
       </c>
       <c r="E15" s="9">
-        <v>18.275</v>
+        <v>30.1</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="9">
+        <v>9.030000000000001</v>
+      </c>
+      <c r="K15" s="14">
+        <v>99.9880237506828</v>
+      </c>
+      <c r="L15" s="14">
+        <v>87.75435717470181</v>
+      </c>
+      <c r="M15" s="14">
+        <v>46.74081989931028</v>
+      </c>
+      <c r="N15" s="19">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2786,16 +4632,34 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="C16" s="8">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="D16" s="8">
-        <v>1.9500000000000002</v>
+        <v>3</v>
       </c>
       <c r="E16" s="8">
-        <v>27.95</v>
+        <v>43</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="8">
+        <v>12.899999999999999</v>
+      </c>
+      <c r="K16" s="13">
+        <v>99.99975019496742</v>
+      </c>
+      <c r="L16" s="13">
+        <v>95.0212931632136</v>
+      </c>
+      <c r="M16" s="13">
+        <v>59.34303402594008</v>
+      </c>
+      <c r="N16" s="18">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2803,16 +4667,34 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>26.25</v>
+        <v>39</v>
       </c>
       <c r="C17" s="8">
-        <v>8.75</v>
+        <v>13</v>
       </c>
       <c r="D17" s="8">
-        <v>2.625</v>
+        <v>3.9000000000000004</v>
       </c>
       <c r="E17" s="8">
-        <v>37.625</v>
+        <v>55.9</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J17" s="8">
+        <v>16.77</v>
+      </c>
+      <c r="K17" s="13">
+        <v>99.99999478947434</v>
+      </c>
+      <c r="L17" s="13">
+        <v>97.97580885541957</v>
+      </c>
+      <c r="M17" s="13">
+        <v>68.9633058734515</v>
+      </c>
+      <c r="N17" s="18">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2820,37 +4702,70 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D18" s="8">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="E18" s="8">
-        <v>47.300000000000004</v>
+        <v>68.80000000000001</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>20.64</v>
+      </c>
+      <c r="K18" s="13">
+        <v>99.99999989131693</v>
+      </c>
+      <c r="L18" s="13">
+        <v>99.17702529509799</v>
+      </c>
+      <c r="M18" s="13">
+        <v>76.30722413178782</v>
+      </c>
+      <c r="N18" s="18">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>38</v>
+      <c r="A20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="K21" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="L21" s="12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2859,16 +4774,28 @@
         <v>0</v>
       </c>
       <c r="B22" s="8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="C22" s="8">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D22" s="8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E22" s="8">
-        <v>86.00000000000001</v>
+        <v>172.00000000000003</v>
+      </c>
+      <c r="I22" s="6">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8">
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="K22" s="8">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="23">
@@ -2876,16 +4803,28 @@
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>127.49999999999999</v>
+        <v>210</v>
       </c>
       <c r="C23" s="9">
-        <v>42.50000000000001</v>
+        <v>70</v>
       </c>
       <c r="D23" s="9">
-        <v>12.75</v>
+        <v>21</v>
       </c>
       <c r="E23" s="9">
-        <v>182.75</v>
+        <v>301</v>
+      </c>
+      <c r="I23" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J23" s="8">
+        <v>6.300000000000001</v>
+      </c>
+      <c r="K23" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0.63</v>
       </c>
     </row>
     <row r="24">
@@ -2893,16 +4832,28 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>195</v>
+        <v>300</v>
       </c>
       <c r="C24" s="8">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D24" s="8">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="E24" s="8">
-        <v>279.5</v>
+        <v>430</v>
+      </c>
+      <c r="I24" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="8">
+        <v>9</v>
+      </c>
+      <c r="K24" s="8">
+        <v>3</v>
+      </c>
+      <c r="L24" s="8">
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -2910,16 +4861,28 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>262.5</v>
+        <v>390</v>
       </c>
       <c r="C25" s="8">
-        <v>87.5</v>
+        <v>130</v>
       </c>
       <c r="D25" s="8">
-        <v>26.25</v>
+        <v>39</v>
       </c>
       <c r="E25" s="8">
-        <v>376.25</v>
+        <v>559</v>
+      </c>
+      <c r="I25" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="J25" s="8">
+        <v>11.7</v>
+      </c>
+      <c r="K25" s="8">
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="L25" s="8">
+        <v>1.17</v>
       </c>
     </row>
     <row r="26">
@@ -2927,88 +4890,155 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="C26" s="8">
-        <v>110.00000000000001</v>
+        <v>160</v>
       </c>
       <c r="D26" s="8">
-        <v>32.99999999999999</v>
+        <v>48</v>
       </c>
       <c r="E26" s="8">
-        <v>473.00000000000006</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6">
-        <v>0</v>
-      </c>
-      <c r="B30" s="8">
-        <v>0.6979018180963897</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="B31" s="8">
-        <v>1.477970605209801</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="B32" s="8">
-        <v>2.2283324147867574</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="B33" s="8">
-        <v>2.9089556865065216</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6">
+        <v>688.0000000000001</v>
+      </c>
+      <c r="I26" s="6">
         <v>1</v>
       </c>
-      <c r="B34" s="8">
-        <v>3.4859223963080885</v>
+      <c r="J26" s="8">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="K26" s="8">
+        <v>4.800000000000001</v>
+      </c>
+      <c r="L26" s="8">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6">
+        <v>0</v>
+      </c>
+      <c r="B49" s="8">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1.032</v>
+      </c>
+      <c r="D49" s="8">
+        <v>2.58</v>
+      </c>
+      <c r="E49" s="8">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="B50" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1.4190000000000003</v>
+      </c>
+      <c r="D50" s="8">
+        <v>3.87</v>
+      </c>
+      <c r="E50" s="8">
+        <v>9.030000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="B51" s="8">
+        <v>0.8639999999999999</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1.8060000000000003</v>
+      </c>
+      <c r="D51" s="8">
+        <v>5.16</v>
+      </c>
+      <c r="E51" s="8">
+        <v>12.899999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="B52" s="8">
+        <v>1.008</v>
+      </c>
+      <c r="C52" s="8">
+        <v>2.1930000000000005</v>
+      </c>
+      <c r="D52" s="8">
+        <v>6.449999999999999</v>
+      </c>
+      <c r="E52" s="8">
+        <v>16.77</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6">
+        <v>1</v>
+      </c>
+      <c r="B53" s="8">
+        <v>1.1520000000000001</v>
+      </c>
+      <c r="C53" s="8">
+        <v>2.58</v>
+      </c>
+      <c r="D53" s="8">
+        <v>7.74</v>
+      </c>
+      <c r="E53" s="8">
+        <v>20.64</v>
       </c>
     </row>
   </sheetData>
@@ -3022,321 +5052,303 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="74.61198425292969" customWidth="1"/>
-    <col min="2" max="2" width="13.5370454788208" customWidth="1"/>
-    <col min="3" max="3" width="13.805088996887207" customWidth="1"/>
-    <col min="4" max="4" width="16.13153839111328" customWidth="1"/>
-    <col min="5" max="5" width="11.337454795837402" customWidth="1"/>
-    <col min="6" max="6" width="13.5155611038208" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="34.38507080078125" customWidth="1"/>
+    <col min="5" max="5" width="13.5370454788208" customWidth="1"/>
+    <col min="6" max="6" width="13.805088996887207" customWidth="1"/>
+    <col min="7" max="7" width="16.13153839111328" customWidth="1"/>
+    <col min="8" max="8" width="11.337454795837402" customWidth="1"/>
+    <col min="9" max="9" width="13.5155611038208" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="s">
-        <v>53</v>
+      <c r="A6" s="15" t="s">
+        <v>62</v>
       </c>
       <c r="B6" s="8">
         <v>0.2</v>
       </c>
+      <c r="D6" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2</v>
+      </c>
+      <c r="G6" s="32">
+        <v>3</v>
+      </c>
+      <c r="H6" s="32">
+        <v>1</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="33">
         <v>0.001</v>
       </c>
+      <c r="D7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="G7" s="32">
+        <v>5</v>
+      </c>
+      <c r="H7" s="32">
+        <v>2</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="s">
-        <v>55</v>
+      <c r="A8" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="B8" s="8">
         <v>1.2</v>
       </c>
+      <c r="D8" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="32">
+        <v>8</v>
+      </c>
+      <c r="H8" s="32">
+        <v>3</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="s">
-        <v>56</v>
+      <c r="A9" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="B9" s="8">
         <v>0.4</v>
       </c>
+      <c r="D9" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="8">
+        <v>5</v>
+      </c>
+      <c r="F9" s="8">
+        <v>4</v>
+      </c>
+      <c r="G9" s="32">
+        <v>10</v>
+      </c>
+      <c r="H9" s="32">
+        <v>5</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="s">
-        <v>57</v>
+      <c r="A10" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="B10" s="8">
         <v>0.12</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="25">
+      <c r="A11" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="25">
+      <c r="A12" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="25">
+      <c r="A13" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="32">
         <v>4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="A14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="32">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="25">
+      <c r="A17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="32">
         <v>60</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="25">
+      <c r="A18" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="32">
         <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>66</v>
+      <c r="A19" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="25">
+      <c r="A20" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="32">
         <v>50</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="25">
+      <c r="A21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="32">
         <v>300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="25">
+      <c r="A24" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="32">
         <v>80</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="25">
+      <c r="A25" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="s">
-        <v>72</v>
+      <c r="A26" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="B26" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="s">
-        <v>73</v>
+      <c r="A27" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="B27" s="8">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="C31" s="8">
-        <v>2</v>
-      </c>
-      <c r="D31" s="25">
-        <v>3</v>
-      </c>
-      <c r="E31" s="25">
-        <v>1</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="8">
-        <v>1</v>
-      </c>
-      <c r="C32" s="8">
-        <v>3</v>
-      </c>
-      <c r="D32" s="25">
-        <v>5</v>
-      </c>
-      <c r="E32" s="25">
-        <v>2</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="C33" s="8">
-        <v>4</v>
-      </c>
-      <c r="D33" s="25">
-        <v>8</v>
-      </c>
-      <c r="E33" s="25">
-        <v>3</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="C34" s="8">
-        <v>5.5</v>
-      </c>
-      <c r="D34" s="25">
-        <v>10</v>
-      </c>
-      <c r="E34" s="25">
-        <v>5</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/docs/balance/balance-realistic.xlsx
+++ b/docs/balance/balance-realistic.xlsx
@@ -1,24 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\OneDrive\Documentos\Stash\repos\FNX Realistic Failures System\RF\docs\balance\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_46830E6391BCBB294114E54D77E51522A8FF1EFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
     <sheet name="Bajo" sheetId="2" r:id="rId2"/>
-    <sheet name="Moderado" sheetId="3" r:id="rId4"/>
-    <sheet name="Alto" sheetId="4" r:id="rId5"/>
-    <sheet name="7700" sheetId="5" r:id="rId6"/>
-    <sheet name="Gráficas" sheetId="6" r:id="rId7"/>
-    <sheet name="Configuración" sheetId="7" r:id="rId8"/>
+    <sheet name="Moderado" sheetId="3" r:id="rId3"/>
+    <sheet name="Alto" sheetId="4" r:id="rId4"/>
+    <sheet name="7700" sheetId="5" r:id="rId5"/>
+    <sheet name="Gráficas" sheetId="6" r:id="rId6"/>
+    <sheet name="Configuración" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="86">
   <si>
     <t>Balance del modo Realistic — generado automáticamente con el motor vigente</t>
   </si>
@@ -281,15 +289,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0 %"/>
-    <numFmt numFmtId="165" formatCode="0.0 &quot; %&quot;"/>
-    <numFmt numFmtId="166" formatCode="0 &quot;vuelos&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0 &quot;h&quot;"/>
+    <numFmt numFmtId="164" formatCode="0\ %"/>
+    <numFmt numFmtId="165" formatCode="0.0\ &quot; %&quot;"/>
+    <numFmt numFmtId="166" formatCode="0\ &quot;vuelos&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0\ &quot;h&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -307,42 +315,42 @@
     <font>
       <i/>
       <sz val="10"/>
-      <color rgb="FF6B7488" tint="0"/>
+      <color rgb="FF6B7488"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF4CAF50" tint="0"/>
+      <color rgb="FF4CAF50"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFE7EBF3" tint="0"/>
+      <color rgb="FFE7EBF3"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF6B7488" tint="0"/>
+      <color rgb="FF6B7488"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFF59E0B" tint="0"/>
+      <color rgb="FFF59E0B"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFEF4444" tint="0"/>
+      <color rgb="FFEF4444"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF8B5CF6" tint="0"/>
+      <color rgb="FF8B5CF6"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -355,12 +363,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF232A38" tint="0"/>
+        <fgColor rgb="FF232A38"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF6FF" tint="0"/>
+        <fgColor rgb="FFEFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -376,62 +384,76 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF1A2029" tint="0"/>
+        <color rgb="FF1A2029"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF1A2029" tint="0"/>
+        <color rgb="FF1A2029"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="2" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="2" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="2" applyNumberFormat="1" fontId="6" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="2" applyNumberFormat="1" fontId="6" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="165" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="166" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="166" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="167" applyNumberFormat="1" fontId="6" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="167" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="168" applyNumberFormat="1" fontId="0" applyFont="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+  <cellXfs count="35">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -443,40 +465,25 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
               <a:t>Perfil Bajo: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Leves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bajo'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bajo'!$J$22:$J$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -485,27 +492,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Bajo!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bajo!$J$22:$J$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.43199999999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.64800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.86399999999999988</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0E91-413D-A801-8344C124E37F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Graves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bajo'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bajo'!$K$22:$K$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -514,27 +565,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Bajo!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bajo!$K$22:$K$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.14400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21599999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.252</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.28800000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0E91-413D-A801-8344C124E37F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Críticas</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bajo'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bajo'!$L$22:$L$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -543,7 +638,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Bajo!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bajo!$L$22:$L$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0E91-413D-A801-8344C124E37F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -556,12 +717,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -571,6 +736,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -579,10 +747,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -593,7 +762,11 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -605,40 +778,25 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
               <a:t>Perfil Moderado: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Leves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Moderado'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Moderado'!$J$22:$J$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -647,27 +805,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Moderado!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Moderado!$J$22:$J$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2600000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.53</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7999999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EF6B-4389-9245-E5CEFE76AC2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Graves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Moderado'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Moderado'!$K$22:$K$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -676,27 +878,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Moderado!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Moderado!$K$22:$K$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.24000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.51000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.60000000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EF6B-4389-9245-E5CEFE76AC2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Críticas</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Moderado'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Moderado'!$L$22:$L$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -705,7 +951,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Moderado!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Moderado!$L$22:$L$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>7.2000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EF6B-4389-9245-E5CEFE76AC2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -718,12 +1030,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -733,6 +1049,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -741,10 +1060,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -755,7 +1075,11 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -767,40 +1091,25 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
               <a:t>Perfil Alto: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Leves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Alto'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Alto'!$J$22:$J$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -809,27 +1118,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Alto!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Alto!$J$22:$J$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.7999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6999999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3999999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9845-459F-8AC7-DCAF68FD781C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Graves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Alto'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Alto'!$K$22:$K$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -838,27 +1191,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Alto!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Alto!$K$22:$K$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.60000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90000000000000013</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8000000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9845-459F-8AC7-DCAF68FD781C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Críticas</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Alto'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Alto'!$L$22:$L$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -867,7 +1264,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Alto!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Alto!$L$22:$L$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.44999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.54</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9845-459F-8AC7-DCAF68FD781C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -880,12 +1343,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -895,6 +1362,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -903,10 +1373,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -917,7 +1388,11 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -929,40 +1404,25 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
               <a:t>Perfil 7700: fallas esperadas por vuelo de 3 h, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Leves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'7700'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'7700'!$J$22:$J$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -971,27 +1431,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$J$22:$J$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.399999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-98F0-4B4A-9FE2-A74D337F6602}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Graves</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'7700'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'7700'!$K$22:$K$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1000,27 +1504,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$K$22:$K$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.2000000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.8000000000000007</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-98F0-4B4A-9FE2-A74D337F6602}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Críticas</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'7700'!$I$22:$I$26</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'7700'!$L$22:$L$26</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1029,7 +1577,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$I$22:$I$26</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$L$22:$L$26</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.17</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-98F0-4B4A-9FE2-A74D337F6602}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -1042,12 +1656,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -1057,6 +1675,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -1065,10 +1686,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1079,7 +1701,11 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1091,40 +1717,26 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
+              <a:rPr lang="en-US"/>
               <a:t>Fallas graves (Major) cada 10 h de vuelo, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Bajo</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bajo'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bajo'!$C$14:$C$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1133,27 +1745,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Bajo!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bajo!$C$14:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.84000000000000008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1ECF-4972-A466-68C310E06B02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Moderado</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Moderado'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Moderado'!$C$14:$C$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1162,27 +1818,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Moderado!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Moderado!$C$14:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.80000000000000016</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1ECF-4972-A466-68C310E06B02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Alto</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Alto'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Alto'!$C$14:$C$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1191,27 +1891,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Alto!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Alto!$C$14:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0000000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1ECF-4972-A466-68C310E06B02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:v>7700</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'7700'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'7700'!$C$14:$C$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1220,7 +1964,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$C$14:$C$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1ECF-4972-A466-68C310E06B02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -1233,12 +2043,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -1248,6 +2062,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -1256,10 +2073,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1270,7 +2088,11 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1282,40 +2104,26 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
+              <a:rPr lang="en-US"/>
               <a:t>Fallas críticas (Critical) cada 100 h de vuelo, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Bajo</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Bajo'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Bajo'!$D$14:$D$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1324,27 +2132,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Bajo!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bajo!$D$14:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-954B-4CED-AE18-0BD32D368CAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Moderado</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Moderado'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Moderado'!$D$14:$D$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1353,27 +2205,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Moderado!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Moderado!$D$14:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-954B-4CED-AE18-0BD32D368CAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Alto</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Alto'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Alto'!$D$14:$D$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1382,27 +2278,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Alto!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Alto!$D$14:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.89999999999999991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7999999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-954B-4CED-AE18-0BD32D368CAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:v>7700</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'7700'!$A$14:$A$18</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'7700'!$D$14:$D$18</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1411,7 +2351,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'7700'!$A$14:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'7700'!$D$14:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.9000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-954B-4CED-AE18-0BD32D368CAA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -1424,12 +2430,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -1439,6 +2449,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -1447,10 +2460,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1461,7 +2475,11 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1473,44 +2491,89 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
+              <a:rPr lang="en-US"/>
               <a:t>Graves cada 10 h por perfil (desgaste 25 %)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Graves / 10 h</c:v>
           </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Resumen'!$A$6:$A$9</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Resumen'!$C$6:$C$9</c:f>
-            </c:numRef>
-          </c:val>
           <c:spPr>
             <a:solidFill>
               <a:srgbClr val="3B82F6"/>
             </a:solidFill>
           </c:spPr>
-        </ser>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Resumen!$A$6:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Bajo</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Moderado</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Alto</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7700</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Resumen!$C$6:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.0000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0000000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C384-4375-A0DB-D19A52AD34A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -1521,12 +2584,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -1536,6 +2603,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -1544,10 +2614,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1558,7 +2629,11 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1570,40 +2645,26 @@
               <a:defRPr sz="1800" b="0"/>
             </a:pPr>
             <a:r>
-              <a:rPr/>
+              <a:rPr lang="en-US"/>
               <a:t>Experiencia por vuelo: fallas esperadas en 3 h, según desgaste</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+        <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Bajo</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Gráficas'!$A$49:$A$53</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Gráficas'!$B$49:$B$53</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1612,27 +2673,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Gráficas!$A$49:$A$53</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Gráficas!$B$49:$B$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.57600000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.86399999999999988</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1520000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3617-4246-8A52-46A182AB81DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:v>Moderado</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Gráficas'!$A$49:$A$53</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Gráficas'!$C$49:$C$53</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1641,27 +2746,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Gráficas!$A$49:$A$53</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Gráficas!$C$49:$C$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.032</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4190000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8060000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.1930000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.58</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3617-4246-8A52-46A182AB81DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:v>Alto</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Gráficas'!$A$49:$A$53</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Gráficas'!$D$49:$D$53</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1670,27 +2819,71 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
-        <ser xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Gráficas!$A$49:$A$53</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Gráficas!$D$49:$D$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.58</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.87</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3617-4246-8A52-46A182AB81DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:v>7700</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="square"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>'Gráficas'!$A$49:$A$53</c:f>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Gráficas'!$E$49:$E$53</c:f>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
           <c:spPr>
             <a:ln>
               <a:solidFill>
@@ -1699,7 +2892,73 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </c:spPr>
-        </ser>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Gráficas!$A$49:$A$53</c:f>
+              <c:numCache>
+                <c:formatCode>0\ %</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Gráficas!$E$49:$E$53</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5.16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0300000000000011</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.77</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.64</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3617-4246-8A52-46A182AB81DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
         <c:axId val="1"/>
@@ -1712,12 +2971,16 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="0\ %" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="2"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2"/>
@@ -1727,6 +2990,9 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="cross"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1"/>
         <c:crosses val="autoZero"/>
@@ -1735,10 +3001,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1746,6 +3013,47 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Experiencia_Bajo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1763,9 +3071,15 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Experiencia_Bajo"/>
+        <xdr:cNvPr id="2" name="Experiencia_Moderado">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1777,8 +3091,8 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
@@ -1798,9 +3112,15 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Experiencia_Moderado"/>
+        <xdr:cNvPr id="2" name="Experiencia_Alto">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1812,8 +3132,8 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
@@ -1833,9 +3153,15 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Experiencia_Alto"/>
+        <xdr:cNvPr id="3" name="Experiencia_7700">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1847,48 +3173,13 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Experiencia_7700"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1903,9 +3194,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="GravesPorDesgaste"/>
+        <xdr:cNvPr id="4" name="GravesPorDesgaste">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1917,8 +3214,8 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1933,9 +3230,15 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="CriticasPorDesgaste"/>
+        <xdr:cNvPr id="5" name="CriticasPorDesgaste">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1947,8 +3250,8 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1963,9 +3266,15 @@
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="GravesPorPerfil"/>
+        <xdr:cNvPr id="6" name="GravesPorPerfil">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1977,8 +3286,8 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1993,9 +3302,15 @@
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="ExperienciaPorDesgaste"/>
+        <xdr:cNvPr id="7" name="ExperienciaPorDesgaste">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2007,43 +3322,388 @@
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.23560333251953" customWidth="1"/>
-    <col min="2" max="2" width="13.4940767288208" customWidth="1"/>
-    <col min="3" max="3" width="12.09656810760498" customWidth="1"/>
-    <col min="4" max="4" width="17.720359802246094" customWidth="1"/>
-    <col min="5" max="5" width="13.865448951721191" customWidth="1"/>
-    <col min="6" max="6" width="20.73737907409668" customWidth="1"/>
-    <col min="9" max="9" width="47.221466064453125" customWidth="1"/>
-    <col min="10" max="10" width="9.505144119262695" customWidth="1"/>
+    <col min="1" max="1" width="65.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="47.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.0315580368042" customWidth="1"/>
-    <col min="13" max="13" width="11.525697708129883" customWidth="1"/>
-    <col min="14" max="14" width="12.009608268737793" customWidth="1"/>
-    <col min="15" max="15" width="13.120657920837402" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2051,3031 +3711,3158 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="12" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>1.7999999999999998</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>0.6</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>0</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>2.4</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>0</v>
       </c>
-      <c r="K6" s="8">
-        <v>0.5760000000000001</v>
-      </c>
-      <c r="L6" s="13">
-        <v>43.78575548031775</v>
-      </c>
-      <c r="M6" s="13">
-        <v>13.4112251940795</v>
-      </c>
-      <c r="N6" s="15" t="s">
+      <c r="K6" s="6">
+        <v>0.57600000000000007</v>
+      </c>
+      <c r="L6" s="11">
+        <v>43.785755480317754</v>
+      </c>
+      <c r="M6" s="11">
+        <v>13.411225194079501</v>
+      </c>
+      <c r="N6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="O6" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>3.3000000000000003</v>
       </c>
-      <c r="C7" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="D7" s="8">
+      <c r="C7" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D7" s="6">
         <v>0.33</v>
       </c>
-      <c r="E7" s="8">
-        <v>4.73</v>
-      </c>
-      <c r="I7" s="28" t="s">
+      <c r="E7" s="6">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="I7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="5">
         <v>0.25</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="7">
         <v>0.72</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="12">
         <v>51.324774404002824</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="12">
         <v>16.4729788588728</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O7" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>9</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>3.0000000000000004</v>
       </c>
-      <c r="D8" s="8">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="D8" s="6">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="E8" s="6">
         <v>12.9</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>1</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="6">
         <v>1.1520000000000001</v>
       </c>
-      <c r="L8" s="13">
-        <v>68.39958713081376</v>
-      </c>
-      <c r="M8" s="13">
+      <c r="L8" s="11">
+        <v>68.399587130813757</v>
+      </c>
+      <c r="M8" s="11">
         <v>25.023840776095874</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="O8" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="25" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>21</v>
       </c>
-      <c r="C9" s="8">
-        <v>7.000000000000001</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="C9" s="6">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="D9" s="6">
         <v>2.1</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>30.1</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>0</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="6">
         <v>1.032</v>
       </c>
-      <c r="L9" s="13">
-        <v>64.37063398138412</v>
-      </c>
-      <c r="M9" s="13">
+      <c r="L9" s="11">
+        <v>64.370633981384117</v>
+      </c>
+      <c r="M9" s="11">
         <v>21.337213893344664</v>
       </c>
-      <c r="N9" s="13">
-        <v>6.946910418879426</v>
-      </c>
-      <c r="O9" s="18">
+      <c r="N9" s="11">
+        <v>6.9469104188794262</v>
+      </c>
+      <c r="O9" s="16">
         <v>14</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="29" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I10" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="5">
         <v>0.25</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="7">
         <v>1.4190000000000003</v>
       </c>
-      <c r="L10" s="14">
-        <v>75.80441481887624</v>
-      </c>
-      <c r="M10" s="14">
+      <c r="L10" s="12">
+        <v>75.804414818876239</v>
+      </c>
+      <c r="M10" s="12">
         <v>28.107626656807383</v>
       </c>
-      <c r="N10" s="14">
-        <v>9.42572919764515</v>
-      </c>
-      <c r="O10" s="19">
+      <c r="N10" s="12">
+        <v>9.4257291976451505</v>
+      </c>
+      <c r="O10" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
-      <c r="I11" s="23" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I11" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
         <v>1</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="6">
         <v>2.58</v>
       </c>
-      <c r="L11" s="13">
-        <v>92.42259959771545</v>
-      </c>
-      <c r="M11" s="13">
-        <v>45.11883639059736</v>
-      </c>
-      <c r="N11" s="13">
+      <c r="L11" s="11">
+        <v>92.422599597715447</v>
+      </c>
+      <c r="M11" s="11">
+        <v>45.118836390597359</v>
+      </c>
+      <c r="N11" s="11">
         <v>16.4729788588728</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="I12" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>0</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="6">
         <v>2.58</v>
       </c>
-      <c r="L12" s="13">
-        <v>92.42259959771545</v>
-      </c>
-      <c r="M12" s="13">
-        <v>45.11883639059736</v>
-      </c>
-      <c r="N12" s="13">
+      <c r="L12" s="11">
+        <v>92.422599597715447</v>
+      </c>
+      <c r="M12" s="11">
+        <v>45.118836390597359</v>
+      </c>
+      <c r="N12" s="11">
         <v>16.4729788588728</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="30" t="s">
+      <c r="I13" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="5">
         <v>0.25</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="7">
         <v>3.87</v>
       </c>
-      <c r="L13" s="14">
-        <v>97.91416305747853</v>
-      </c>
-      <c r="M13" s="14">
-        <v>59.3430340259401</v>
-      </c>
-      <c r="N13" s="14">
+      <c r="L13" s="12">
+        <v>97.914163057478532</v>
+      </c>
+      <c r="M13" s="12">
+        <v>59.343034025940099</v>
+      </c>
+      <c r="N13" s="12">
         <v>23.662050566314687</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="17">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>0.72</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>0.48</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>0.96</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <v>0</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="24">
         <v>0</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I14" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="6">
         <v>7.74</v>
       </c>
-      <c r="L14" s="13">
-        <v>99.95649284249212</v>
-      </c>
-      <c r="M14" s="13">
+      <c r="L14" s="11">
+        <v>99.956492842492125</v>
+      </c>
+      <c r="M14" s="11">
         <v>83.47011117784136</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="11">
         <v>41.725174762601036</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>1.4000000000000001</v>
       </c>
-      <c r="C15" s="8">
-        <v>0.8000000000000002</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="6">
+        <v>0.80000000000000016</v>
+      </c>
+      <c r="D15" s="6">
         <v>2</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <v>0.42000000000000004</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="25">
         <v>30.3</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>0</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="6">
         <v>5.16</v>
       </c>
-      <c r="L15" s="13">
-        <v>99.42583003143459</v>
-      </c>
-      <c r="M15" s="13">
-        <v>69.8805788087798</v>
-      </c>
-      <c r="N15" s="13">
+      <c r="L15" s="11">
+        <v>99.425830031434586</v>
+      </c>
+      <c r="M15" s="11">
+        <v>69.880578808779802</v>
+      </c>
+      <c r="N15" s="11">
         <v>30.232367392896897</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>4</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>2</v>
       </c>
-      <c r="D16" s="8">
-        <v>6.000000000000001</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="D16" s="6">
+        <v>6.0000000000000009</v>
+      </c>
+      <c r="E16" s="6">
         <v>1.2</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="25">
         <v>11.1</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="5">
         <v>0.25</v>
       </c>
-      <c r="K16" s="9">
-        <v>9.030000000000001</v>
-      </c>
-      <c r="L16" s="14">
+      <c r="K16" s="7">
+        <v>9.0300000000000011</v>
+      </c>
+      <c r="L16" s="12">
         <v>99.9880237506828</v>
       </c>
-      <c r="M16" s="14">
-        <v>87.75435717470181</v>
-      </c>
-      <c r="N16" s="14">
-        <v>46.74081989931028</v>
-      </c>
-      <c r="O16" s="19">
+      <c r="M16" s="12">
+        <v>87.754357174701809</v>
+      </c>
+      <c r="N16" s="12">
+        <v>46.740819899310281</v>
+      </c>
+      <c r="O16" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>4</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>16</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <v>3</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="25">
         <v>4.8</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="4">
         <v>1</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="6">
         <v>20.64</v>
       </c>
-      <c r="L17" s="13">
-        <v>99.99999989131693</v>
-      </c>
-      <c r="M17" s="13">
-        <v>99.17702529509799</v>
-      </c>
-      <c r="N17" s="13">
-        <v>76.30722413178782</v>
-      </c>
-      <c r="O17" s="18">
+      <c r="L17" s="11">
+        <v>99.999999891316932</v>
+      </c>
+      <c r="M17" s="11">
+        <v>99.177025295097991</v>
+      </c>
+      <c r="N17" s="11">
+        <v>76.307224131787819</v>
+      </c>
+      <c r="O17" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="30">
         <v>84</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="30">
         <v>167</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="30">
         <v>267</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="30">
         <v>28</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="30">
         <v>56</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="30">
         <v>89</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="30">
         <v>14</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="30">
         <v>28</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="30">
         <v>45</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
-    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
-    <col min="11" max="11" width="10.435111045837402" customWidth="1"/>
-    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
-    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
-    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="54" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>0</v>
       </c>
-      <c r="B6" s="8">
-        <v>0.144</v>
-      </c>
-      <c r="C6" s="8">
-        <v>0.048</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="B6" s="6">
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="C6" s="6">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D6" s="8">
         <v>0</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>0.192</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>0</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="6">
         <v>0.15424029807434747</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>0.25</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>0.18</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>0.06</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>0</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>0.24</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.25</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="6">
         <v>0.18892925754788115</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>0.5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>0.216</v>
       </c>
-      <c r="C8" s="8">
-        <v>0.072</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="6">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="D8" s="8">
         <v>0</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.288</v>
-      </c>
-      <c r="I8" s="6">
+      <c r="E8" s="6">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="I8" s="4">
         <v>0.5</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="6">
         <v>0.22219544420944856</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>0.75</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>0.252</v>
       </c>
-      <c r="C9" s="8">
-        <v>0.084</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="C9" s="6">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="D9" s="8">
         <v>0</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.336</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="E9" s="6">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="I9" s="4">
         <v>0.75</v>
       </c>
-      <c r="J9" s="8">
-        <v>0.254097213296716</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
+      <c r="J9" s="6">
+        <v>0.25409721329671597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
-        <v>0.288</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0.096</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="B10" s="6">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="C10" s="6">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="D10" s="8">
         <v>0</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.384</v>
-      </c>
-      <c r="I10" s="6">
+      <c r="E10" s="6">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="I10" s="4">
         <v>1</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="6">
         <v>0.28469052659863137</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>0</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>1.44</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>0.48</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="8">
         <v>0</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <v>1.92</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>0</v>
       </c>
-      <c r="J14" s="8">
-        <v>0.5760000000000001</v>
-      </c>
-      <c r="K14" s="13">
-        <v>43.78575548031775</v>
-      </c>
-      <c r="L14" s="13">
-        <v>13.4112251940795</v>
-      </c>
-      <c r="M14" s="15" t="s">
+      <c r="J14" s="6">
+        <v>0.57600000000000007</v>
+      </c>
+      <c r="K14" s="11">
+        <v>43.785755480317754</v>
+      </c>
+      <c r="L14" s="11">
+        <v>13.411225194079501</v>
+      </c>
+      <c r="M14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="15" t="s">
+      <c r="N14" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>0.25</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>1.7999999999999998</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <v>0.6</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="9">
         <v>0</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>2.4</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>0.25</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="7">
         <v>0.72</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="12">
         <v>51.324774404002824</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="12">
         <v>16.4729788588728</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="N15" s="16" t="s">
+      <c r="N15" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>0.5</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>2.16</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>0.72</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>0</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <v>2.88</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="4">
         <v>0.5</v>
       </c>
-      <c r="J16" s="8">
-        <v>0.8639999999999999</v>
-      </c>
-      <c r="K16" s="13">
-        <v>57.85271852240823</v>
-      </c>
-      <c r="L16" s="13">
+      <c r="J16" s="6">
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="K16" s="11">
+        <v>57.852718522408232</v>
+      </c>
+      <c r="L16" s="11">
         <v>19.426469812652037</v>
       </c>
-      <c r="M16" s="15" t="s">
+      <c r="M16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="15" t="s">
+      <c r="N16" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>0.75</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>2.52</v>
       </c>
-      <c r="C17" s="8">
-        <v>0.8400000000000001</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="C17" s="6">
+        <v>0.84000000000000008</v>
+      </c>
+      <c r="D17" s="8">
         <v>0</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <v>3.3600000000000003</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="4">
         <v>0.75</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="6">
         <v>1.008</v>
       </c>
-      <c r="K17" s="13">
-        <v>63.50518535455063</v>
-      </c>
-      <c r="L17" s="13">
-        <v>22.27552619310539</v>
-      </c>
-      <c r="M17" s="15" t="s">
+      <c r="K17" s="11">
+        <v>63.505185354550633</v>
+      </c>
+      <c r="L17" s="11">
+        <v>22.275526193105389</v>
+      </c>
+      <c r="M17" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N17" s="15" t="s">
+      <c r="N17" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>2.88</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <v>0.96</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>0</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="6">
         <v>3.84</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="4">
         <v>1</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <v>1.1520000000000001</v>
       </c>
-      <c r="K18" s="13">
-        <v>68.39958713081376</v>
-      </c>
-      <c r="L18" s="13">
+      <c r="K18" s="11">
+        <v>68.399587130813757</v>
+      </c>
+      <c r="L18" s="11">
         <v>25.023840776095874</v>
       </c>
-      <c r="M18" s="15" t="s">
+      <c r="M18" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N18" s="15" t="s">
+      <c r="N18" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>0</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>14.399999999999999</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>4.8</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="8">
         <v>0</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="6">
         <v>19.2</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="4">
         <v>0</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <v>0.43199999999999994</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <v>0.14400000000000002</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>0.25</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>18</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>6</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="9">
         <v>0</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>24</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="4">
         <v>0.25</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="6">
         <v>0.54</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="6">
         <v>0.18</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>0.5</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>21.6</v>
       </c>
-      <c r="C24" s="8">
-        <v>7.199999999999999</v>
-      </c>
-      <c r="D24" s="10">
+      <c r="C24" s="6">
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="D24" s="8">
         <v>0</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <v>28.799999999999997</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="4">
         <v>0.5</v>
       </c>
-      <c r="J24" s="8">
-        <v>0.648</v>
-      </c>
-      <c r="K24" s="8">
+      <c r="J24" s="6">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="K24" s="6">
         <v>0.21599999999999997</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>0.75</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>25.2</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>8.4</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="8">
         <v>0</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="6">
         <v>33.6</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="4">
         <v>0.75</v>
       </c>
-      <c r="J25" s="8">
-        <v>0.756</v>
-      </c>
-      <c r="K25" s="8">
+      <c r="J25" s="6">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="K25" s="6">
         <v>0.252</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>28.799999999999997</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>9.6</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <v>0</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="6">
         <v>38.4</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="4">
         <v>1</v>
       </c>
-      <c r="J26" s="8">
-        <v>0.8639999999999999</v>
-      </c>
-      <c r="K26" s="8">
+      <c r="J26" s="6">
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="K26" s="6">
         <v>0.28800000000000003</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
-    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
-    <col min="11" max="11" width="10.435111045837402" customWidth="1"/>
-    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
-    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
-    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="54" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>0.24</v>
       </c>
-      <c r="C6" s="8">
-        <v>0.08000000000000002</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.024</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="C6" s="6">
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2.4E-2</v>
+      </c>
+      <c r="E6" s="6">
         <v>0.34400000000000003</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>0</v>
       </c>
-      <c r="J6" s="8">
-        <v>0.2760390792579295</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7">
+      <c r="J6" s="6">
+        <v>0.27603907925792948</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>0.25</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>0.33</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>0.11000000000000001</v>
       </c>
-      <c r="D7" s="9">
-        <v>0.033</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0.4730000000000001</v>
-      </c>
-      <c r="I7" s="6">
+      <c r="D7" s="7">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.47300000000000009</v>
+      </c>
+      <c r="I7" s="4">
         <v>0.25</v>
       </c>
-      <c r="J7" s="8">
-        <v>0.3760884077067357</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6">
+      <c r="J7" s="6">
+        <v>0.37608840770673568</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>0.5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>0.42000000000000004</v>
       </c>
-      <c r="C8" s="8">
-        <v>0.14</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.042</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.6020000000000001</v>
-      </c>
-      <c r="I8" s="6">
+      <c r="C8" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.60200000000000009</v>
+      </c>
+      <c r="I8" s="4">
         <v>0.5</v>
       </c>
-      <c r="J8" s="8">
-        <v>0.473282045782378</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6">
+      <c r="J8" s="6">
+        <v>0.47328204578237798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>0.75</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>0.51</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>0.17000000000000004</v>
       </c>
-      <c r="D9" s="8">
-        <v>0.051000000000000004</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.7310000000000001</v>
-      </c>
-      <c r="I9" s="6">
+      <c r="D9" s="6">
+        <v>5.1000000000000004E-2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.73100000000000009</v>
+      </c>
+      <c r="I9" s="4">
         <v>0.75</v>
       </c>
-      <c r="J9" s="8">
-        <v>0.5671991056391092</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
+      <c r="J9" s="6">
+        <v>0.56719910563910925</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>0.6</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>0.2</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>0.06</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>0.8600000000000001</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="4">
         <v>1</v>
       </c>
-      <c r="J10" s="8">
-        <v>0.6575305947099431</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="s">
+      <c r="J10" s="6">
+        <v>0.65753059470994313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>0</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>2.4</v>
       </c>
-      <c r="C14" s="8">
-        <v>0.8000000000000002</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="6">
+        <v>0.80000000000000016</v>
+      </c>
+      <c r="D14" s="6">
         <v>0.24</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <v>3.4400000000000004</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>0</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <v>1.032</v>
       </c>
-      <c r="K14" s="13">
-        <v>64.37063398138412</v>
-      </c>
-      <c r="L14" s="13">
+      <c r="K14" s="11">
+        <v>64.370633981384117</v>
+      </c>
+      <c r="L14" s="11">
         <v>21.337213893344664</v>
       </c>
-      <c r="M14" s="13">
-        <v>6.946910418879426</v>
-      </c>
-      <c r="N14" s="18">
+      <c r="M14" s="11">
+        <v>6.9469104188794262</v>
+      </c>
+      <c r="N14" s="16">
         <v>14</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>0.25</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>3.3000000000000003</v>
       </c>
-      <c r="C15" s="9">
-        <v>1.1</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="C15" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D15" s="7">
         <v>0.33</v>
       </c>
-      <c r="E15" s="9">
-        <v>4.73</v>
-      </c>
-      <c r="I15" s="7">
+      <c r="E15" s="7">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="I15" s="5">
         <v>0.25</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="7">
         <v>1.4190000000000003</v>
       </c>
-      <c r="K15" s="14">
-        <v>75.80441481887624</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="K15" s="12">
+        <v>75.804414818876239</v>
+      </c>
+      <c r="L15" s="12">
         <v>28.107626656807383</v>
       </c>
-      <c r="M15" s="14">
-        <v>9.42572919764515</v>
-      </c>
-      <c r="N15" s="19">
+      <c r="M15" s="12">
+        <v>9.4257291976451505</v>
+      </c>
+      <c r="N15" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>0.5</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>4.2</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>1.4000000000000001</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>0.42000000000000004</v>
       </c>
-      <c r="E16" s="8">
-        <v>6.020000000000001</v>
-      </c>
-      <c r="I16" s="6">
+      <c r="E16" s="6">
+        <v>6.0200000000000014</v>
+      </c>
+      <c r="I16" s="4">
         <v>0.5</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="6">
         <v>1.8060000000000003</v>
       </c>
-      <c r="K16" s="13">
-        <v>83.56899356695996</v>
-      </c>
-      <c r="L16" s="13">
-        <v>34.29531801849433</v>
-      </c>
-      <c r="M16" s="13">
+      <c r="K16" s="11">
+        <v>83.568993566959961</v>
+      </c>
+      <c r="L16" s="11">
+        <v>34.295318018494328</v>
+      </c>
+      <c r="M16" s="11">
         <v>11.838515321658393</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="16">
         <v>8</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>0.75</v>
       </c>
-      <c r="B17" s="8">
-        <v>5.1</v>
-      </c>
-      <c r="C17" s="8">
+      <c r="B17" s="6">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C17" s="6">
         <v>1.7000000000000004</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>0.51</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <v>7.3100000000000005</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="4">
         <v>0.75</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="6">
         <v>2.1930000000000005</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="11">
         <v>88.84184985064023</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="11">
         <v>39.95044211877341</v>
       </c>
-      <c r="M17" s="13">
-        <v>14.18702781886062</v>
-      </c>
-      <c r="N17" s="18">
+      <c r="M17" s="11">
+        <v>14.187027818860621</v>
+      </c>
+      <c r="N17" s="16">
         <v>7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>6</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <v>2</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>0.6</v>
       </c>
-      <c r="E18" s="8">
-        <v>8.600000000000001</v>
-      </c>
-      <c r="I18" s="6">
+      <c r="E18" s="6">
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="I18" s="4">
         <v>1</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <v>2.58</v>
       </c>
-      <c r="K18" s="13">
-        <v>92.42259959771545</v>
-      </c>
-      <c r="L18" s="13">
-        <v>45.11883639059736</v>
-      </c>
-      <c r="M18" s="13">
+      <c r="K18" s="11">
+        <v>92.422599597715447</v>
+      </c>
+      <c r="L18" s="11">
+        <v>45.118836390597359</v>
+      </c>
+      <c r="M18" s="11">
         <v>16.4729788588728</v>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>0</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>24</v>
       </c>
-      <c r="C22" s="8">
-        <v>8.000000000000002</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="6">
+        <v>8.0000000000000018</v>
+      </c>
+      <c r="D22" s="6">
         <v>2.4</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="6">
         <v>34.400000000000006</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="4">
         <v>0</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <v>0.72</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <v>0.24000000000000005</v>
       </c>
-      <c r="L22" s="8">
-        <v>0.07200000000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7">
+      <c r="L22" s="6">
+        <v>7.2000000000000008E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>0.25</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>33</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>11.000000000000002</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>3.3000000000000003</v>
       </c>
-      <c r="E23" s="9">
-        <v>47.30000000000001</v>
-      </c>
-      <c r="I23" s="6">
+      <c r="E23" s="7">
+        <v>47.300000000000011</v>
+      </c>
+      <c r="I23" s="4">
         <v>0.25</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="6">
         <v>0.99</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="6">
         <v>0.33000000000000007</v>
       </c>
-      <c r="L23" s="8">
-        <v>0.099</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6">
+      <c r="L23" s="6">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>0.5</v>
       </c>
-      <c r="B24" s="8">
-        <v>42.00000000000001</v>
-      </c>
-      <c r="C24" s="8">
+      <c r="B24" s="6">
+        <v>42.000000000000007</v>
+      </c>
+      <c r="C24" s="6">
         <v>14.000000000000002</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>4.2</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <v>60.20000000000001</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="4">
         <v>0.5</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="6">
         <v>1.2600000000000002</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="6">
         <v>0.42000000000000004</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="6">
         <v>0.126</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>0.75</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>51</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>17.000000000000004</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>5.1000000000000005</v>
       </c>
-      <c r="E25" s="8">
-        <v>73.10000000000001</v>
-      </c>
-      <c r="I25" s="6">
+      <c r="E25" s="6">
+        <v>73.100000000000009</v>
+      </c>
+      <c r="I25" s="4">
         <v>0.75</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="6">
         <v>1.53</v>
       </c>
-      <c r="K25" s="8">
-        <v>0.5100000000000001</v>
-      </c>
-      <c r="L25" s="8">
+      <c r="K25" s="6">
+        <v>0.51000000000000012</v>
+      </c>
+      <c r="L25" s="6">
         <v>0.15300000000000002</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>60</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>20</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>6</v>
       </c>
-      <c r="E26" s="8">
-        <v>86.00000000000001</v>
-      </c>
-      <c r="I26" s="6">
+      <c r="E26" s="6">
+        <v>86.000000000000014</v>
+      </c>
+      <c r="I26" s="4">
         <v>1</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="6">
         <v>1.7999999999999998</v>
       </c>
-      <c r="K26" s="8">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="L26" s="8">
+      <c r="K26" s="6">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="L26" s="6">
         <v>0.18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
-    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
-    <col min="11" max="11" width="10.435111045837402" customWidth="1"/>
-    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
-    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
-    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="54" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>0.6</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>0.2</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>0.06</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>0.8600000000000001</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>0</v>
       </c>
-      <c r="J6" s="8">
-        <v>0.6914293040316685</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7">
+      <c r="J6" s="6">
+        <v>0.69142930403166847</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>0.25</v>
       </c>
-      <c r="B7" s="9">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="7">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="C7" s="7">
         <v>0.30000000000000004</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>0.09</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>1.29</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.25</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="6">
         <v>1.0196826013476679</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>0.5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>1.2</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>0.4</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>0.12</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>1.7200000000000002</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>0.5</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="6">
         <v>1.3247366613101321</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>0.75</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>1.5</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>0.5</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>0.15</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>2.15</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>0.75</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="6">
         <v>1.6006548428410656</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>1.7999999999999998</v>
       </c>
-      <c r="C10" s="8">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="6">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="D10" s="6">
         <v>0.18</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>2.58</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="4">
         <v>1</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="6">
         <v>1.8443946434174783</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>0</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>6</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>2</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>0.6</v>
       </c>
-      <c r="E14" s="8">
-        <v>8.600000000000001</v>
-      </c>
-      <c r="I14" s="6">
+      <c r="E14" s="6">
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="I14" s="4">
         <v>0</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <v>2.58</v>
       </c>
-      <c r="K14" s="13">
-        <v>92.42259959771545</v>
-      </c>
-      <c r="L14" s="13">
-        <v>45.11883639059736</v>
-      </c>
-      <c r="M14" s="13">
+      <c r="K14" s="11">
+        <v>92.422599597715447</v>
+      </c>
+      <c r="L14" s="11">
+        <v>45.118836390597359</v>
+      </c>
+      <c r="M14" s="11">
         <v>16.4729788588728</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="16">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>0.25</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>9</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <v>3.0000000000000004</v>
       </c>
-      <c r="D15" s="9">
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="E15" s="9">
+      <c r="D15" s="7">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="E15" s="7">
         <v>12.9</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>0.25</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="7">
         <v>3.87</v>
       </c>
-      <c r="K15" s="14">
-        <v>97.91416305747853</v>
-      </c>
-      <c r="L15" s="14">
-        <v>59.3430340259401</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="K15" s="12">
+        <v>97.914163057478532</v>
+      </c>
+      <c r="L15" s="12">
+        <v>59.343034025940099</v>
+      </c>
+      <c r="M15" s="12">
         <v>23.662050566314687</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="17">
         <v>4</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>0.5</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>12</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>4</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>1.2</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <v>17.200000000000003</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="4">
         <v>0.5</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="6">
         <v>5.16</v>
       </c>
-      <c r="K16" s="13">
-        <v>99.42583003143459</v>
-      </c>
-      <c r="L16" s="13">
-        <v>69.8805788087798</v>
-      </c>
-      <c r="M16" s="13">
+      <c r="K16" s="11">
+        <v>99.425830031434586</v>
+      </c>
+      <c r="L16" s="11">
+        <v>69.880578808779802</v>
+      </c>
+      <c r="M16" s="11">
         <v>30.232367392896897</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N16" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>0.75</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>5</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>1.5</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <v>21.5</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="4">
         <v>0.75</v>
       </c>
-      <c r="J17" s="8">
-        <v>6.449999999999999</v>
-      </c>
-      <c r="K17" s="13">
-        <v>99.84194778312639</v>
-      </c>
-      <c r="L17" s="13">
-        <v>77.68698398515703</v>
-      </c>
-      <c r="M17" s="13">
-        <v>36.23718483782267</v>
-      </c>
-      <c r="N17" s="18">
+      <c r="J17" s="6">
+        <v>6.4499999999999993</v>
+      </c>
+      <c r="K17" s="11">
+        <v>99.841947783126386</v>
+      </c>
+      <c r="L17" s="11">
+        <v>77.686983985157028</v>
+      </c>
+      <c r="M17" s="11">
+        <v>36.237184837822667</v>
+      </c>
+      <c r="N17" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>18</v>
       </c>
-      <c r="C18" s="8">
-        <v>6.000000000000001</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="6">
+        <v>6.0000000000000009</v>
+      </c>
+      <c r="D18" s="6">
         <v>1.7999999999999998</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="6">
         <v>25.8</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="4">
         <v>1</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <v>7.74</v>
       </c>
-      <c r="K18" s="13">
-        <v>99.95649284249212</v>
-      </c>
-      <c r="L18" s="13">
+      <c r="K18" s="11">
+        <v>99.956492842492125</v>
+      </c>
+      <c r="L18" s="11">
         <v>83.47011117784136</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="11">
         <v>41.725174762601036</v>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="16">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="20" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>0</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>60</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>20</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>6</v>
       </c>
-      <c r="E22" s="8">
-        <v>86.00000000000001</v>
-      </c>
-      <c r="I22" s="6">
+      <c r="E22" s="6">
+        <v>86.000000000000014</v>
+      </c>
+      <c r="I22" s="4">
         <v>0</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <v>1.7999999999999998</v>
       </c>
-      <c r="K22" s="8">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="L22" s="8">
+      <c r="K22" s="6">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="L22" s="6">
         <v>0.18</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>0.25</v>
       </c>
-      <c r="B23" s="9">
-        <v>89.99999999999999</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="B23" s="7">
+        <v>89.999999999999986</v>
+      </c>
+      <c r="C23" s="7">
         <v>30.000000000000004</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>9</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>129</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="4">
         <v>0.25</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="6">
         <v>2.6999999999999997</v>
       </c>
-      <c r="K23" s="8">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="L23" s="8">
+      <c r="K23" s="6">
+        <v>0.90000000000000013</v>
+      </c>
+      <c r="L23" s="6">
         <v>0.27</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>0.5</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>120</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="6">
         <v>40</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>12</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <v>172.00000000000003</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="4">
         <v>0.5</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="6">
         <v>3.5999999999999996</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="6">
         <v>1.2000000000000002</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="6">
         <v>0.36</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>0.75</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>150</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>50</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>15</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="6">
         <v>215</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="4">
         <v>0.75</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="6">
         <v>4.5</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="6">
         <v>1.5</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="6">
         <v>0.44999999999999996</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>179.99999999999997</v>
       </c>
-      <c r="C26" s="8">
-        <v>60.00000000000001</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="C26" s="6">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="D26" s="6">
         <v>18</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="6">
         <v>258</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="4">
         <v>1</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="6">
         <v>5.3999999999999995</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="6">
         <v>1.8000000000000003</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="6">
         <v>0.54</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.435016632080078" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="9" max="9" width="53.99211502075195" customWidth="1"/>
-    <col min="10" max="10" width="13.83680248260498" customWidth="1"/>
-    <col min="11" max="11" width="11.0315580368042" customWidth="1"/>
-    <col min="12" max="12" width="11.525697708129883" customWidth="1"/>
-    <col min="13" max="13" width="12.009608268737793" customWidth="1"/>
-    <col min="14" max="14" width="13.120657920837402" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="5" width="9.140625" customWidth="1"/>
+    <col min="9" max="9" width="54" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>1.2</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>0.4</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>0.12</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>1.7200000000000002</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>0</v>
       </c>
-      <c r="J6" s="8">
-        <v>1.39210782937486</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7">
+      <c r="J6" s="6">
+        <v>1.3921078293748601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>0.25</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>2.1</v>
       </c>
-      <c r="C7" s="9">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="7">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="D7" s="7">
         <v>0.21</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>3.0100000000000002</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.25</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="6">
         <v>2.387038545299486</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>0.5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>0.3</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>4.3</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>0.5</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="6">
         <v>3.2437256854769796</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>0.75</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>3.9</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>1.3</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>0.39</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>5.59</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>0.75</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="6">
         <v>3.8993720091628767</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>1</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>4.8</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>1.6</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>0.48</v>
       </c>
-      <c r="E10" s="8">
-        <v>6.880000000000001</v>
-      </c>
-      <c r="I10" s="6">
+      <c r="E10" s="6">
+        <v>6.8800000000000008</v>
+      </c>
+      <c r="I10" s="4">
         <v>1</v>
       </c>
-      <c r="J10" s="8">
-        <v>4.351241580084704</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="s">
+      <c r="J10" s="6">
+        <v>4.3512415800847037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>39</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
         <v>0</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>12</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>4</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>1.2</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <v>17.200000000000003</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>0</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="6">
         <v>5.16</v>
       </c>
-      <c r="K14" s="13">
-        <v>99.42583003143459</v>
-      </c>
-      <c r="L14" s="13">
-        <v>69.8805788087798</v>
-      </c>
-      <c r="M14" s="13">
+      <c r="K14" s="11">
+        <v>99.425830031434586</v>
+      </c>
+      <c r="L14" s="11">
+        <v>69.880578808779802</v>
+      </c>
+      <c r="M14" s="11">
         <v>30.232367392896897</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>0.25</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <v>21</v>
       </c>
-      <c r="C15" s="9">
-        <v>7.000000000000001</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="C15" s="7">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="D15" s="7">
         <v>2.1</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>30.1</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>0.25</v>
       </c>
-      <c r="J15" s="9">
-        <v>9.030000000000001</v>
-      </c>
-      <c r="K15" s="14">
+      <c r="J15" s="7">
+        <v>9.0300000000000011</v>
+      </c>
+      <c r="K15" s="12">
         <v>99.9880237506828</v>
       </c>
-      <c r="L15" s="14">
-        <v>87.75435717470181</v>
-      </c>
-      <c r="M15" s="14">
-        <v>46.74081989931028</v>
-      </c>
-      <c r="N15" s="19">
+      <c r="L15" s="12">
+        <v>87.754357174701809</v>
+      </c>
+      <c r="M15" s="12">
+        <v>46.740819899310281</v>
+      </c>
+      <c r="N15" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>0.5</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>30</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>10</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>3</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <v>43</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="4">
         <v>0.5</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="6">
         <v>12.899999999999999</v>
       </c>
-      <c r="K16" s="13">
-        <v>99.99975019496742</v>
-      </c>
-      <c r="L16" s="13">
-        <v>95.0212931632136</v>
-      </c>
-      <c r="M16" s="13">
-        <v>59.34303402594008</v>
-      </c>
-      <c r="N16" s="18">
+      <c r="K16" s="11">
+        <v>99.999750194967419</v>
+      </c>
+      <c r="L16" s="11">
+        <v>95.021293163213599</v>
+      </c>
+      <c r="M16" s="11">
+        <v>59.343034025940078</v>
+      </c>
+      <c r="N16" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>0.75</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="6">
         <v>39</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>13</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>3.9000000000000004</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="6">
         <v>55.9</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="4">
         <v>0.75</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="6">
         <v>16.77</v>
       </c>
-      <c r="K17" s="13">
-        <v>99.99999478947434</v>
-      </c>
-      <c r="L17" s="13">
-        <v>97.97580885541957</v>
-      </c>
-      <c r="M17" s="13">
-        <v>68.9633058734515</v>
-      </c>
-      <c r="N17" s="18">
+      <c r="K17" s="11">
+        <v>99.999994789474343</v>
+      </c>
+      <c r="L17" s="11">
+        <v>97.975808855419572</v>
+      </c>
+      <c r="M17" s="11">
+        <v>68.963305873451503</v>
+      </c>
+      <c r="N17" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="6">
         <v>48</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <v>16</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>4.8</v>
       </c>
-      <c r="E18" s="8">
-        <v>68.80000000000001</v>
-      </c>
-      <c r="I18" s="6">
+      <c r="E18" s="6">
+        <v>68.800000000000011</v>
+      </c>
+      <c r="I18" s="4">
         <v>1</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="6">
         <v>20.64</v>
       </c>
-      <c r="K18" s="13">
-        <v>99.99999989131693</v>
-      </c>
-      <c r="L18" s="13">
-        <v>99.17702529509799</v>
-      </c>
-      <c r="M18" s="13">
-        <v>76.30722413178782</v>
-      </c>
-      <c r="N18" s="18">
+      <c r="K18" s="11">
+        <v>99.999999891316932</v>
+      </c>
+      <c r="L18" s="11">
+        <v>99.177025295097991</v>
+      </c>
+      <c r="M18" s="11">
+        <v>76.307224131787819</v>
+      </c>
+      <c r="N18" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="21" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>41</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>0</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>120</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="6">
         <v>40</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>12</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="6">
         <v>172.00000000000003</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="4">
         <v>0</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="6">
         <v>3.5999999999999996</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <v>1.2000000000000002</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="6">
         <v>0.36</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>0.25</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <v>210</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>70</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="7">
         <v>21</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="7">
         <v>301</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="4">
         <v>0.25</v>
       </c>
-      <c r="J23" s="8">
-        <v>6.300000000000001</v>
-      </c>
-      <c r="K23" s="8">
+      <c r="J23" s="6">
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="K23" s="6">
         <v>2.1</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="6">
         <v>0.63</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>0.5</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="6">
         <v>300</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="6">
         <v>100</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>30</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <v>430</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="4">
         <v>0.5</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="6">
         <v>9</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="6">
         <v>3</v>
       </c>
-      <c r="L24" s="8">
-        <v>0.8999999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6">
+      <c r="L24" s="6">
+        <v>0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>0.75</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="6">
         <v>390</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="6">
         <v>130</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>39</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="6">
         <v>559</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="4">
         <v>0.75</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="6">
         <v>11.7</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="6">
         <v>3.9000000000000004</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="6">
         <v>1.17</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>1</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>480</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="6">
         <v>160</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>48</v>
       </c>
-      <c r="E26" s="8">
-        <v>688.0000000000001</v>
-      </c>
-      <c r="I26" s="6">
+      <c r="E26" s="6">
+        <v>688.00000000000011</v>
+      </c>
+      <c r="I26" s="4">
         <v>1</v>
       </c>
-      <c r="J26" s="8">
+      <c r="J26" s="6">
         <v>14.399999999999999</v>
       </c>
-      <c r="K26" s="8">
-        <v>4.800000000000001</v>
-      </c>
-      <c r="L26" s="8">
+      <c r="K26" s="6">
+        <v>4.8000000000000007</v>
+      </c>
+      <c r="L26" s="6">
         <v>1.44</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
         <v>0</v>
       </c>
-      <c r="B49" s="8">
-        <v>0.5760000000000001</v>
-      </c>
-      <c r="C49" s="8">
+      <c r="B49" s="6">
+        <v>0.57600000000000007</v>
+      </c>
+      <c r="C49" s="6">
         <v>1.032</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="6">
         <v>2.58</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="6">
         <v>5.16</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
         <v>0.25</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="6">
         <v>0.72</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="6">
         <v>1.4190000000000003</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="6">
         <v>3.87</v>
       </c>
-      <c r="E50" s="8">
-        <v>9.030000000000001</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6">
+      <c r="E50" s="6">
+        <v>9.0300000000000011</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
         <v>0.5</v>
       </c>
-      <c r="B51" s="8">
-        <v>0.8639999999999999</v>
-      </c>
-      <c r="C51" s="8">
+      <c r="B51" s="6">
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="C51" s="6">
         <v>1.8060000000000003</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="6">
         <v>5.16</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="6">
         <v>12.899999999999999</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
         <v>0.75</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="6">
         <v>1.008</v>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="6">
         <v>2.1930000000000005</v>
       </c>
-      <c r="D52" s="8">
-        <v>6.449999999999999</v>
-      </c>
-      <c r="E52" s="8">
+      <c r="D52" s="6">
+        <v>6.4499999999999993</v>
+      </c>
+      <c r="E52" s="6">
         <v>16.77</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
         <v>1</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="6">
         <v>1.1520000000000001</v>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="6">
         <v>2.58</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="6">
         <v>7.74</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="6">
         <v>20.64</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="74.61198425292969" customWidth="1"/>
+    <col min="1" max="1" width="74.5703125" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="34.38507080078125" customWidth="1"/>
-    <col min="5" max="5" width="13.5370454788208" customWidth="1"/>
-    <col min="6" max="6" width="13.805088996887207" customWidth="1"/>
-    <col min="7" max="7" width="16.13153839111328" customWidth="1"/>
-    <col min="8" max="8" width="11.337454795837402" customWidth="1"/>
-    <col min="9" max="9" width="13.5155611038208" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>53</v>
       </c>
@@ -5083,279 +6870,279 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>0.2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>0.6</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>2</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <v>3</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="30">
         <v>1</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="33">
-        <v>0.001</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>2.5</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="30">
         <v>5</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="30">
         <v>2</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="13" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>1.2</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>2.5</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>3</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="30">
         <v>8</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>3</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>0.4</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>5</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>4</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>10</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="30">
         <v>5</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>0.12</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="30">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="30">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="30">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="30">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="30">
         <v>60</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="30">
         <v>5</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="30">
         <v>50</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="30">
         <v>300</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="30">
         <v>80</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="30">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="6">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/balance/balance-realistic.xlsx
+++ b/docs/balance/balance-realistic.xlsx
@@ -152,13 +152,13 @@
     <t>Perfil Moderado (nivel 2)</t>
   </si>
   <si>
-    <t>Multiplicador ×1 · desgaste máx ×2 · tope agravación 5 · tope tierra 2 · tregua crítica 120 min</t>
+    <t>Multiplicador ×1,1 · desgaste máx ×2 · tope agravación 5 · tope tierra 2 · tregua crítica 120 min</t>
   </si>
   <si>
     <t>Perfil Alto (nivel 3)</t>
   </si>
   <si>
-    <t>Multiplicador ×1,4 · desgaste máx ×2,5 · tope agravación 8 · tope tierra 3 · tregua crítica 60 min</t>
+    <t>Multiplicador ×1,6 · desgaste máx ×2,5 · tope agravación 8 · tope tierra 3 · tregua crítica 60 min</t>
   </si>
   <si>
     <t>Perfil 7700 (nivel 4)</t>
@@ -2094,16 +2094,16 @@
         <v>15</v>
       </c>
       <c r="B6" s="8">
-        <v>1.125</v>
+        <v>0.375</v>
       </c>
       <c r="C6" s="8">
-        <v>0.44999999999999996</v>
+        <v>0.15</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
       </c>
       <c r="E6" s="8">
-        <v>1.5749999999999997</v>
+        <v>0.525</v>
       </c>
       <c r="I6" s="22" t="s">
         <v>15</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <v>0.378</v>
+        <v>0.126</v>
       </c>
       <c r="L6" s="13">
-        <v>31.476949933412968</v>
+        <v>11.838515321658393</v>
       </c>
       <c r="M6" s="13">
-        <v>10.237240356956512</v>
+        <v>3.535970651687692</v>
       </c>
       <c r="N6" s="15" t="s">
         <v>16</v>
@@ -2132,16 +2132,16 @@
         <v>17</v>
       </c>
       <c r="B7" s="8">
-        <v>1.875</v>
+        <v>0.6875</v>
       </c>
       <c r="C7" s="8">
-        <v>0.7500000000000001</v>
+        <v>0.275</v>
       </c>
       <c r="D7" s="8">
-        <v>0.22499999999999998</v>
+        <v>0.09625000000000002</v>
       </c>
       <c r="E7" s="8">
-        <v>2.8500000000000005</v>
+        <v>1.0587499999999999</v>
       </c>
       <c r="I7" s="28" t="s">
         <v>15</v>
@@ -2150,13 +2150,13 @@
         <v>0.25</v>
       </c>
       <c r="K7" s="9">
-        <v>0.4724999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="L7" s="14">
-        <v>37.65582858825108</v>
+        <v>14.572318639152048</v>
       </c>
       <c r="M7" s="14">
-        <v>12.628408831196559</v>
+        <v>4.4002518166900035</v>
       </c>
       <c r="N7" s="16" t="s">
         <v>16</v>
@@ -2170,16 +2170,16 @@
         <v>18</v>
       </c>
       <c r="B8" s="8">
-        <v>2.8875</v>
+        <v>1.1</v>
       </c>
       <c r="C8" s="8">
-        <v>1.155</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="D8" s="8">
-        <v>0.34650000000000003</v>
+        <v>0.15400000000000003</v>
       </c>
       <c r="E8" s="8">
-        <v>4.389</v>
+        <v>1.6940000000000002</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>15</v>
@@ -2188,13 +2188,13 @@
         <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>0.756</v>
+        <v>0.252</v>
       </c>
       <c r="L8" s="13">
-        <v>53.04591609572007</v>
+        <v>22.27552619310539</v>
       </c>
       <c r="M8" s="13">
-        <v>19.426469812652037</v>
+        <v>6.946910418879426</v>
       </c>
       <c r="N8" s="15" t="s">
         <v>16</v>
@@ -2208,16 +2208,16 @@
         <v>19</v>
       </c>
       <c r="B9" s="8">
-        <v>5.775</v>
+        <v>1.9250000000000003</v>
       </c>
       <c r="C9" s="8">
-        <v>2.31</v>
+        <v>0.7700000000000001</v>
       </c>
       <c r="D9" s="8">
-        <v>0.6930000000000001</v>
+        <v>0.2695000000000001</v>
       </c>
       <c r="E9" s="8">
-        <v>8.778</v>
+        <v>2.964500000000001</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>17</v>
@@ -2226,19 +2226,19 @@
         <v>0</v>
       </c>
       <c r="K9" s="8">
-        <v>0.6839999999999999</v>
+        <v>0.25410000000000005</v>
       </c>
       <c r="L9" s="13">
-        <v>49.54054280664488</v>
+        <v>22.438576325539895</v>
       </c>
       <c r="M9" s="13">
-        <v>16.4729788588728</v>
+        <v>6.386913570838115</v>
       </c>
       <c r="N9" s="13">
-        <v>5.256789349820168</v>
+        <v>2.2835237588950674</v>
       </c>
       <c r="O9" s="18">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -2249,19 +2249,19 @@
         <v>0.25</v>
       </c>
       <c r="K10" s="9">
-        <v>0.8550000000000001</v>
+        <v>0.317625</v>
       </c>
       <c r="L10" s="14">
-        <v>57.47168089177259</v>
+        <v>27.21243093737824</v>
       </c>
       <c r="M10" s="14">
-        <v>20.148378124062294</v>
+        <v>7.918856214319547</v>
       </c>
       <c r="N10" s="14">
-        <v>6.527227938397251</v>
+        <v>2.8462100885829456</v>
       </c>
       <c r="O10" s="19">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -2272,19 +2272,19 @@
         <v>1</v>
       </c>
       <c r="K11" s="8">
-        <v>1.3679999999999999</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="L11" s="13">
-        <v>74.53843179751962</v>
+        <v>39.84225557590899</v>
       </c>
       <c r="M11" s="13">
-        <v>30.232367392896897</v>
+        <v>12.365900492062675</v>
       </c>
       <c r="N11" s="13">
-        <v>10.237240356956512</v>
+        <v>4.514902710215763</v>
       </c>
       <c r="O11" s="18">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -2298,19 +2298,19 @@
         <v>0</v>
       </c>
       <c r="K12" s="8">
-        <v>0.9576</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="L12" s="13">
-        <v>61.61870674843213</v>
+        <v>30.89893203642754</v>
       </c>
       <c r="M12" s="13">
-        <v>22.27552619310539</v>
+        <v>9.153598393129393</v>
       </c>
       <c r="N12" s="13">
-        <v>7.28129928028104</v>
+        <v>3.3041789424606893</v>
       </c>
       <c r="O12" s="18">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -2339,19 +2339,19 @@
         <v>0.25</v>
       </c>
       <c r="K13" s="9">
-        <v>1.3167</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="L13" s="14">
-        <v>73.19816953846153</v>
+        <v>39.84225557590899</v>
       </c>
       <c r="M13" s="14">
-        <v>29.284118071272868</v>
+        <v>12.365900492062675</v>
       </c>
       <c r="N13" s="14">
-        <v>9.872964018737374</v>
+        <v>4.514902710215763</v>
       </c>
       <c r="O13" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -2359,13 +2359,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="8">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="C14" s="8">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="D14" s="8">
-        <v>0.72</v>
+        <v>0.24</v>
       </c>
       <c r="E14" s="10">
         <v>0</v>
@@ -2380,19 +2380,19 @@
         <v>1</v>
       </c>
       <c r="K14" s="8">
-        <v>2.394</v>
+        <v>0.9240000000000002</v>
       </c>
       <c r="L14" s="13">
-        <v>90.87361027969408</v>
+        <v>60.307185117411755</v>
       </c>
       <c r="M14" s="13">
-        <v>46.74081989931028</v>
+        <v>21.337213893344664</v>
       </c>
       <c r="N14" s="13">
-        <v>17.221349330526635</v>
+        <v>8.056874390487534</v>
       </c>
       <c r="O14" s="18">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -2400,19 +2400,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="8">
-        <v>0.9</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="C15" s="8">
-        <v>0.6</v>
+        <v>0.22000000000000006</v>
       </c>
       <c r="D15" s="8">
-        <v>1.2</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="E15" s="8">
-        <v>0.27</v>
+        <v>0.11550000000000002</v>
       </c>
       <c r="F15" s="27">
-        <v>44.4</v>
+        <v>103.9</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>19</v>
@@ -2421,19 +2421,19 @@
         <v>0</v>
       </c>
       <c r="K15" s="8">
-        <v>1.5048000000000001</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="L15" s="13">
-        <v>77.79382982686424</v>
+        <v>39.84225557590899</v>
       </c>
       <c r="M15" s="13">
-        <v>32.69933040626136</v>
+        <v>12.365900492062675</v>
       </c>
       <c r="N15" s="13">
-        <v>11.201461992055773</v>
+        <v>4.514902710215763</v>
       </c>
       <c r="O15" s="18">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -2441,19 +2441,19 @@
         <v>18</v>
       </c>
       <c r="B16" s="8">
-        <v>1.47</v>
+        <v>0.5600000000000002</v>
       </c>
       <c r="C16" s="8">
-        <v>0.8400000000000001</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="D16" s="8">
-        <v>2.1</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="E16" s="8">
-        <v>0.441</v>
+        <v>0.19600000000000004</v>
       </c>
       <c r="F16" s="27">
-        <v>28.9</v>
+        <v>64.9</v>
       </c>
       <c r="I16" s="31" t="s">
         <v>19</v>
@@ -2462,19 +2462,19 @@
         <v>0.25</v>
       </c>
       <c r="K16" s="9">
-        <v>2.6334</v>
+        <v>0.8893500000000003</v>
       </c>
       <c r="L16" s="14">
-        <v>92.8166188391095</v>
+        <v>58.907723423853874</v>
       </c>
       <c r="M16" s="14">
-        <v>49.99264043042324</v>
+        <v>20.62605339647573</v>
       </c>
       <c r="N16" s="14">
-        <v>18.771173852321922</v>
+        <v>7.766796912647744</v>
       </c>
       <c r="O16" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -2482,19 +2482,19 @@
         <v>19</v>
       </c>
       <c r="B17" s="8">
-        <v>3.3000000000000007</v>
+        <v>1.1</v>
       </c>
       <c r="C17" s="8">
-        <v>1.32</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="D17" s="8">
-        <v>5.28</v>
+        <v>1.7600000000000005</v>
       </c>
       <c r="E17" s="8">
-        <v>0.9899999999999999</v>
+        <v>0.3850000000000001</v>
       </c>
       <c r="F17" s="27">
-        <v>14.4</v>
+        <v>37.1</v>
       </c>
       <c r="I17" s="25" t="s">
         <v>19</v>
@@ -2503,19 +2503,19 @@
         <v>1</v>
       </c>
       <c r="K17" s="8">
-        <v>6.0192000000000005</v>
+        <v>2.0328000000000004</v>
       </c>
       <c r="L17" s="13">
-        <v>99.75683858915977</v>
+        <v>86.90317039556565</v>
       </c>
       <c r="M17" s="13">
-        <v>79.48471565820229</v>
+        <v>41.02166423871496</v>
       </c>
       <c r="N17" s="13">
-        <v>37.8239308109401</v>
+        <v>16.87294786679101</v>
       </c>
       <c r="O17" s="18">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2652,22 +2652,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="8">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="C6" s="8">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
       </c>
       <c r="E6" s="8">
-        <v>0.126</v>
+        <v>0.041999999999999996</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="8">
-        <v>0.13649880716424506</v>
+        <v>0.5854493017231386</v>
       </c>
     </row>
     <row r="7">
@@ -2675,22 +2675,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>0.11249999999999999</v>
+        <v>0.0375</v>
       </c>
       <c r="C7" s="9">
-        <v>0.045</v>
+        <v>0.015</v>
       </c>
       <c r="D7" s="11">
         <v>0</v>
       </c>
       <c r="E7" s="9">
-        <v>0.15749999999999997</v>
+        <v>0.0525</v>
       </c>
       <c r="I7" s="6">
         <v>0.25</v>
       </c>
       <c r="J7" s="8">
-        <v>0.1676065056278613</v>
+        <v>0.6673618445261195</v>
       </c>
     </row>
     <row r="8">
@@ -2698,22 +2698,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>0.135</v>
+        <v>0.045</v>
       </c>
       <c r="C8" s="8">
-        <v>0.054000000000000006</v>
+        <v>0.018</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
       </c>
       <c r="E8" s="8">
-        <v>0.189</v>
+        <v>0.063</v>
       </c>
       <c r="I8" s="6">
         <v>0.5</v>
       </c>
       <c r="J8" s="8">
-        <v>0.1975935468049191</v>
+        <v>0.7330889974688497</v>
       </c>
     </row>
     <row r="9">
@@ -2721,22 +2721,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>0.1575</v>
+        <v>0.0525</v>
       </c>
       <c r="C9" s="8">
-        <v>0.063</v>
+        <v>0.021</v>
       </c>
       <c r="D9" s="10">
         <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>0.2205</v>
+        <v>0.0735</v>
       </c>
       <c r="I9" s="6">
         <v>0.75</v>
       </c>
       <c r="J9" s="8">
-        <v>0.2265003024624068</v>
+        <v>0.7858288891402363</v>
       </c>
     </row>
     <row r="10">
@@ -2744,22 +2744,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="C10" s="8">
-        <v>0.072</v>
+        <v>0.024</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
       </c>
       <c r="E10" s="8">
-        <v>0.252</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="I10" s="6">
         <v>1</v>
       </c>
       <c r="J10" s="8">
-        <v>0.25436568997122827</v>
+        <v>0.8281477185581665</v>
       </c>
     </row>
     <row r="12">
@@ -2810,28 +2810,28 @@
         <v>0</v>
       </c>
       <c r="B14" s="8">
-        <v>0.8999999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="C14" s="8">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="D14" s="10">
         <v>0</v>
       </c>
       <c r="E14" s="8">
-        <v>1.26</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>0.378</v>
+        <v>0.126</v>
       </c>
       <c r="K14" s="13">
-        <v>31.476949933412968</v>
+        <v>11.838515321658393</v>
       </c>
       <c r="L14" s="13">
-        <v>10.237240356956512</v>
+        <v>3.535970651687692</v>
       </c>
       <c r="M14" s="15" t="s">
         <v>16</v>
@@ -2845,28 +2845,28 @@
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>1.125</v>
+        <v>0.375</v>
       </c>
       <c r="C15" s="9">
-        <v>0.44999999999999996</v>
+        <v>0.15</v>
       </c>
       <c r="D15" s="11">
         <v>0</v>
       </c>
       <c r="E15" s="9">
-        <v>1.5749999999999997</v>
+        <v>0.525</v>
       </c>
       <c r="I15" s="7">
         <v>0.25</v>
       </c>
       <c r="J15" s="9">
-        <v>0.4724999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="K15" s="14">
-        <v>37.65582858825108</v>
+        <v>14.572318639152048</v>
       </c>
       <c r="L15" s="14">
-        <v>12.628408831196559</v>
+        <v>4.4002518166900035</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>16</v>
@@ -2880,28 +2880,28 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>1.35</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="C16" s="8">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="D16" s="10">
         <v>0</v>
       </c>
       <c r="E16" s="8">
-        <v>1.8900000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="I16" s="6">
         <v>0.5</v>
       </c>
       <c r="J16" s="8">
-        <v>0.567</v>
+        <v>0.189</v>
       </c>
       <c r="K16" s="13">
-        <v>43.27754375731159</v>
+        <v>17.221349330526635</v>
       </c>
       <c r="L16" s="13">
-        <v>14.955879545976703</v>
+        <v>5.256789349820168</v>
       </c>
       <c r="M16" s="15" t="s">
         <v>16</v>
@@ -2915,28 +2915,28 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>1.575</v>
+        <v>0.525</v>
       </c>
       <c r="C17" s="8">
-        <v>0.63</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="D17" s="10">
         <v>0</v>
       </c>
       <c r="E17" s="8">
-        <v>2.205</v>
+        <v>0.735</v>
       </c>
       <c r="I17" s="6">
         <v>0.75</v>
       </c>
       <c r="J17" s="8">
-        <v>0.6615</v>
+        <v>0.22049999999999997</v>
       </c>
       <c r="K17" s="13">
-        <v>48.392336134290694</v>
+        <v>19.788236113836998</v>
       </c>
       <c r="L17" s="13">
-        <v>17.221349330526635</v>
+        <v>6.105652631086677</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>16</v>
@@ -2950,28 +2950,28 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>1.7999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="C18" s="8">
-        <v>0.72</v>
+        <v>0.24</v>
       </c>
       <c r="D18" s="10">
         <v>0</v>
       </c>
       <c r="E18" s="8">
-        <v>2.52</v>
+        <v>0.8399999999999999</v>
       </c>
       <c r="I18" s="6">
         <v>1</v>
       </c>
       <c r="J18" s="8">
-        <v>0.756</v>
+        <v>0.252</v>
       </c>
       <c r="K18" s="13">
-        <v>53.04591609572007</v>
+        <v>22.27552619310539</v>
       </c>
       <c r="L18" s="13">
-        <v>19.426469812652037</v>
+        <v>6.946910418879426</v>
       </c>
       <c r="M18" s="15" t="s">
         <v>16</v>
@@ -3022,25 +3022,25 @@
         <v>0</v>
       </c>
       <c r="B22" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C22" s="8">
-        <v>3.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="D22" s="10">
         <v>0</v>
       </c>
       <c r="E22" s="8">
-        <v>12.6</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
       </c>
       <c r="J22" s="8">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="K22" s="8">
-        <v>0.10799999999999998</v>
+        <v>0.036000000000000004</v>
       </c>
       <c r="L22" s="10">
         <v>0</v>
@@ -3051,25 +3051,25 @@
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>11.249999999999998</v>
+        <v>3.75</v>
       </c>
       <c r="C23" s="9">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="D23" s="11">
         <v>0</v>
       </c>
       <c r="E23" s="9">
-        <v>15.749999999999996</v>
+        <v>5.25</v>
       </c>
       <c r="I23" s="6">
         <v>0.25</v>
       </c>
       <c r="J23" s="8">
-        <v>0.33749999999999997</v>
+        <v>0.11249999999999999</v>
       </c>
       <c r="K23" s="8">
-        <v>0.135</v>
+        <v>0.045</v>
       </c>
       <c r="L23" s="10">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="C24" s="8">
-        <v>5.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D24" s="10">
         <v>0</v>
       </c>
       <c r="E24" s="8">
-        <v>18.9</v>
+        <v>6.3</v>
       </c>
       <c r="I24" s="6">
         <v>0.5</v>
       </c>
       <c r="J24" s="8">
-        <v>0.405</v>
+        <v>0.135</v>
       </c>
       <c r="K24" s="8">
-        <v>0.16200000000000003</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="L24" s="10">
         <v>0</v>
@@ -3109,25 +3109,25 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>15.75</v>
+        <v>5.25</v>
       </c>
       <c r="C25" s="8">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="D25" s="10">
         <v>0</v>
       </c>
       <c r="E25" s="8">
-        <v>22.05</v>
+        <v>7.35</v>
       </c>
       <c r="I25" s="6">
         <v>0.75</v>
       </c>
       <c r="J25" s="8">
-        <v>0.47250000000000003</v>
+        <v>0.1575</v>
       </c>
       <c r="K25" s="8">
-        <v>0.189</v>
+        <v>0.063</v>
       </c>
       <c r="L25" s="10">
         <v>0</v>
@@ -3138,25 +3138,25 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C26" s="8">
-        <v>7.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="D26" s="10">
         <v>0</v>
       </c>
       <c r="E26" s="8">
-        <v>25.2</v>
+        <v>8.399999999999999</v>
       </c>
       <c r="I26" s="6">
         <v>1</v>
       </c>
       <c r="J26" s="8">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="K26" s="8">
-        <v>0.21599999999999997</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="L26" s="10">
         <v>0</v>
@@ -3236,22 +3236,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="8">
-        <v>0.15</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="C6" s="8">
-        <v>0.06</v>
+        <v>0.022000000000000006</v>
       </c>
       <c r="D6" s="8">
-        <v>0.018</v>
+        <v>0.007700000000000002</v>
       </c>
       <c r="E6" s="8">
-        <v>0.22799999999999998</v>
+        <v>0.08470000000000001</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="8">
-        <v>0.24243850945225734</v>
+        <v>1.280677297141557</v>
       </c>
     </row>
     <row r="7">
@@ -3259,22 +3259,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>0.1875</v>
+        <v>0.06875</v>
       </c>
       <c r="C7" s="9">
-        <v>0.07500000000000001</v>
+        <v>0.027500000000000004</v>
       </c>
       <c r="D7" s="9">
-        <v>0.0225</v>
+        <v>0.009625000000000002</v>
       </c>
       <c r="E7" s="9">
-        <v>0.28500000000000003</v>
+        <v>0.105875</v>
       </c>
       <c r="I7" s="6">
         <v>0.25</v>
       </c>
       <c r="J7" s="8">
-        <v>0.30165201826261484</v>
+        <v>1.4659031971398768</v>
       </c>
     </row>
     <row r="8">
@@ -3282,22 +3282,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>0.22499999999999998</v>
+        <v>0.08250000000000002</v>
       </c>
       <c r="C8" s="8">
-        <v>0.09</v>
+        <v>0.03300000000000001</v>
       </c>
       <c r="D8" s="8">
-        <v>0.026999999999999996</v>
+        <v>0.011550000000000003</v>
       </c>
       <c r="E8" s="8">
-        <v>0.34199999999999997</v>
+        <v>0.12705000000000002</v>
       </c>
       <c r="I8" s="6">
         <v>0.5</v>
       </c>
       <c r="J8" s="8">
-        <v>0.3600248618302144</v>
+        <v>1.6074345281085254</v>
       </c>
     </row>
     <row r="9">
@@ -3305,22 +3305,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>0.2625</v>
+        <v>0.09625000000000002</v>
       </c>
       <c r="C9" s="8">
-        <v>0.10500000000000001</v>
+        <v>0.038500000000000006</v>
       </c>
       <c r="D9" s="8">
-        <v>0.0315</v>
+        <v>0.013475000000000004</v>
       </c>
       <c r="E9" s="8">
-        <v>0.399</v>
+        <v>0.14822500000000005</v>
       </c>
       <c r="I9" s="6">
         <v>0.75</v>
       </c>
       <c r="J9" s="8">
-        <v>0.4174484238549685</v>
+        <v>1.7138652206118348</v>
       </c>
     </row>
     <row r="10">
@@ -3328,22 +3328,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>0.3</v>
+        <v>0.11000000000000001</v>
       </c>
       <c r="C10" s="8">
-        <v>0.12</v>
+        <v>0.04400000000000001</v>
       </c>
       <c r="D10" s="8">
-        <v>0.036</v>
+        <v>0.015400000000000004</v>
       </c>
       <c r="E10" s="8">
-        <v>0.45599999999999996</v>
+        <v>0.16940000000000002</v>
       </c>
       <c r="I10" s="6">
         <v>1</v>
       </c>
       <c r="J10" s="8">
-        <v>0.4738299317857949</v>
+        <v>1.792899996514622</v>
       </c>
     </row>
     <row r="12">
@@ -3394,34 +3394,34 @@
         <v>0</v>
       </c>
       <c r="B14" s="8">
-        <v>1.5</v>
+        <v>0.55</v>
       </c>
       <c r="C14" s="8">
-        <v>0.6</v>
+        <v>0.22000000000000006</v>
       </c>
       <c r="D14" s="8">
-        <v>0.18</v>
+        <v>0.07700000000000001</v>
       </c>
       <c r="E14" s="8">
-        <v>2.28</v>
+        <v>0.8470000000000001</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>0.6839999999999999</v>
+        <v>0.25410000000000005</v>
       </c>
       <c r="K14" s="13">
-        <v>49.54054280664488</v>
+        <v>22.438576325539895</v>
       </c>
       <c r="L14" s="13">
-        <v>16.4729788588728</v>
+        <v>6.386913570838115</v>
       </c>
       <c r="M14" s="13">
-        <v>5.256789349820168</v>
+        <v>2.2835237588950674</v>
       </c>
       <c r="N14" s="18">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
@@ -3429,34 +3429,34 @@
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>1.875</v>
+        <v>0.6875</v>
       </c>
       <c r="C15" s="9">
-        <v>0.7500000000000001</v>
+        <v>0.275</v>
       </c>
       <c r="D15" s="9">
-        <v>0.22499999999999998</v>
+        <v>0.09625000000000002</v>
       </c>
       <c r="E15" s="9">
-        <v>2.8500000000000005</v>
+        <v>1.0587499999999999</v>
       </c>
       <c r="I15" s="7">
         <v>0.25</v>
       </c>
       <c r="J15" s="9">
-        <v>0.8550000000000001</v>
+        <v>0.317625</v>
       </c>
       <c r="K15" s="14">
-        <v>57.47168089177259</v>
+        <v>27.21243093737824</v>
       </c>
       <c r="L15" s="14">
-        <v>20.148378124062294</v>
+        <v>7.918856214319547</v>
       </c>
       <c r="M15" s="14">
-        <v>6.527227938397251</v>
+        <v>2.8462100885829456</v>
       </c>
       <c r="N15" s="19">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3464,34 +3464,34 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>2.25</v>
+        <v>0.8250000000000002</v>
       </c>
       <c r="C16" s="8">
-        <v>0.8999999999999999</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="D16" s="8">
-        <v>0.26999999999999996</v>
+        <v>0.11550000000000003</v>
       </c>
       <c r="E16" s="8">
-        <v>3.42</v>
+        <v>1.2705000000000002</v>
       </c>
       <c r="I16" s="6">
         <v>0.5</v>
       </c>
       <c r="J16" s="8">
-        <v>1.0259999999999998</v>
+        <v>0.3811500000000001</v>
       </c>
       <c r="K16" s="13">
-        <v>64.1562151721006</v>
+        <v>31.692457937817643</v>
       </c>
       <c r="L16" s="13">
-        <v>23.662050566314687</v>
+        <v>9.42572919764515</v>
       </c>
       <c r="M16" s="13">
-        <v>7.7806308555391945</v>
+        <v>3.405656269651103</v>
       </c>
       <c r="N16" s="18">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -3499,34 +3499,34 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>2.625</v>
+        <v>0.9625000000000001</v>
       </c>
       <c r="C17" s="8">
-        <v>1.05</v>
+        <v>0.38500000000000006</v>
       </c>
       <c r="D17" s="8">
-        <v>0.315</v>
+        <v>0.13475000000000004</v>
       </c>
       <c r="E17" s="8">
-        <v>3.99</v>
+        <v>1.4822500000000005</v>
       </c>
       <c r="I17" s="6">
         <v>0.75</v>
       </c>
       <c r="J17" s="8">
-        <v>1.197</v>
+        <v>0.44467500000000015</v>
       </c>
       <c r="K17" s="13">
-        <v>69.79008487217166</v>
+        <v>35.896742223077204</v>
       </c>
       <c r="L17" s="13">
-        <v>27.02111257309432</v>
+        <v>10.90794277629219</v>
       </c>
       <c r="M17" s="13">
-        <v>9.017226537397004</v>
+        <v>3.961880960031161</v>
       </c>
       <c r="N17" s="18">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -3534,34 +3534,34 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="C18" s="8">
-        <v>1.2</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="D18" s="8">
-        <v>0.36</v>
+        <v>0.15400000000000003</v>
       </c>
       <c r="E18" s="8">
-        <v>4.56</v>
+        <v>1.6940000000000002</v>
       </c>
       <c r="I18" s="6">
         <v>1</v>
       </c>
       <c r="J18" s="8">
-        <v>1.3679999999999999</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="K18" s="13">
-        <v>74.53843179751962</v>
+        <v>39.84225557590899</v>
       </c>
       <c r="L18" s="13">
-        <v>30.232367392896897</v>
+        <v>12.365900492062675</v>
       </c>
       <c r="M18" s="13">
-        <v>10.237240356956512</v>
+        <v>4.514902710215763</v>
       </c>
       <c r="N18" s="18">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -3606,28 +3606,28 @@
         <v>0</v>
       </c>
       <c r="B22" s="8">
-        <v>15</v>
+        <v>5.500000000000001</v>
       </c>
       <c r="C22" s="8">
-        <v>6</v>
+        <v>2.2000000000000006</v>
       </c>
       <c r="D22" s="8">
-        <v>1.7999999999999998</v>
+        <v>0.7700000000000002</v>
       </c>
       <c r="E22" s="8">
-        <v>22.799999999999997</v>
+        <v>8.47</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
       </c>
       <c r="J22" s="8">
-        <v>0.44999999999999996</v>
+        <v>0.16500000000000004</v>
       </c>
       <c r="K22" s="8">
-        <v>0.18</v>
+        <v>0.06600000000000002</v>
       </c>
       <c r="L22" s="8">
-        <v>0.05399999999999999</v>
+        <v>0.023100000000000006</v>
       </c>
     </row>
     <row r="23">
@@ -3635,28 +3635,28 @@
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>18.75</v>
+        <v>6.875000000000001</v>
       </c>
       <c r="C23" s="9">
-        <v>7.500000000000001</v>
+        <v>2.7500000000000004</v>
       </c>
       <c r="D23" s="9">
-        <v>2.25</v>
+        <v>0.9625000000000001</v>
       </c>
       <c r="E23" s="9">
-        <v>28.500000000000004</v>
+        <v>10.5875</v>
       </c>
       <c r="I23" s="6">
         <v>0.25</v>
       </c>
       <c r="J23" s="8">
-        <v>0.5625</v>
+        <v>0.20625000000000002</v>
       </c>
       <c r="K23" s="8">
-        <v>0.22500000000000003</v>
+        <v>0.08250000000000002</v>
       </c>
       <c r="L23" s="8">
-        <v>0.0675</v>
+        <v>0.028875000000000005</v>
       </c>
     </row>
     <row r="24">
@@ -3664,28 +3664,28 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>22.499999999999996</v>
+        <v>8.250000000000002</v>
       </c>
       <c r="C24" s="8">
-        <v>9</v>
+        <v>3.3000000000000007</v>
       </c>
       <c r="D24" s="8">
-        <v>2.6999999999999997</v>
+        <v>1.1550000000000002</v>
       </c>
       <c r="E24" s="8">
-        <v>34.199999999999996</v>
+        <v>12.705000000000002</v>
       </c>
       <c r="I24" s="6">
         <v>0.5</v>
       </c>
       <c r="J24" s="8">
-        <v>0.6749999999999999</v>
+        <v>0.24750000000000005</v>
       </c>
       <c r="K24" s="8">
-        <v>0.27</v>
+        <v>0.09900000000000003</v>
       </c>
       <c r="L24" s="8">
-        <v>0.08099999999999999</v>
+        <v>0.03465000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3693,28 +3693,28 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>26.25</v>
+        <v>9.625000000000002</v>
       </c>
       <c r="C25" s="8">
-        <v>10.500000000000002</v>
+        <v>3.8500000000000005</v>
       </c>
       <c r="D25" s="8">
-        <v>3.15</v>
+        <v>1.3475000000000004</v>
       </c>
       <c r="E25" s="8">
-        <v>39.900000000000006</v>
+        <v>14.822500000000005</v>
       </c>
       <c r="I25" s="6">
         <v>0.75</v>
       </c>
       <c r="J25" s="8">
-        <v>0.7875000000000001</v>
+        <v>0.28875000000000006</v>
       </c>
       <c r="K25" s="8">
-        <v>0.31500000000000006</v>
+        <v>0.11550000000000002</v>
       </c>
       <c r="L25" s="8">
-        <v>0.0945</v>
+        <v>0.040425000000000016</v>
       </c>
     </row>
     <row r="26">
@@ -3722,28 +3722,28 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>30</v>
+        <v>11.000000000000002</v>
       </c>
       <c r="C26" s="8">
-        <v>12</v>
+        <v>4.400000000000001</v>
       </c>
       <c r="D26" s="8">
-        <v>3.5999999999999996</v>
+        <v>1.5400000000000005</v>
       </c>
       <c r="E26" s="8">
-        <v>45.599999999999994</v>
+        <v>16.94</v>
       </c>
       <c r="I26" s="6">
         <v>1</v>
       </c>
       <c r="J26" s="8">
-        <v>0.8999999999999999</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="K26" s="8">
-        <v>0.36</v>
+        <v>0.13200000000000003</v>
       </c>
       <c r="L26" s="8">
-        <v>0.10799999999999998</v>
+        <v>0.04620000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3820,22 +3820,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="8">
-        <v>0.21</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="C6" s="8">
-        <v>0.084</v>
+        <v>0.03200000000000001</v>
       </c>
       <c r="D6" s="8">
-        <v>0.025199999999999997</v>
+        <v>0.011200000000000003</v>
       </c>
       <c r="E6" s="8">
-        <v>0.3192</v>
+        <v>0.12320000000000002</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="8">
-        <v>0.3419723512641555</v>
+        <v>2.001246508334804</v>
       </c>
     </row>
     <row r="7">
@@ -3843,22 +3843,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>0.28875</v>
+        <v>0.11000000000000001</v>
       </c>
       <c r="C7" s="9">
-        <v>0.1155</v>
+        <v>0.04400000000000001</v>
       </c>
       <c r="D7" s="9">
-        <v>0.03465</v>
+        <v>0.015400000000000004</v>
       </c>
       <c r="E7" s="9">
-        <v>0.4389</v>
+        <v>0.16940000000000002</v>
       </c>
       <c r="I7" s="6">
         <v>0.25</v>
       </c>
       <c r="J7" s="8">
-        <v>0.46930409321289246</v>
+        <v>2.4189578700817855</v>
       </c>
     </row>
     <row r="8">
@@ -3866,22 +3866,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>0.3675</v>
+        <v>0.14</v>
       </c>
       <c r="C8" s="8">
-        <v>0.147</v>
+        <v>0.05600000000000001</v>
       </c>
       <c r="D8" s="8">
-        <v>0.0441</v>
+        <v>0.019600000000000003</v>
       </c>
       <c r="E8" s="8">
-        <v>0.5586</v>
+        <v>0.2156</v>
       </c>
       <c r="I8" s="6">
         <v>0.5</v>
       </c>
       <c r="J8" s="8">
-        <v>0.5954918817616139</v>
+        <v>2.677163704132067</v>
       </c>
     </row>
     <row r="9">
@@ -3889,22 +3889,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>0.44625</v>
+        <v>0.17000000000000004</v>
       </c>
       <c r="C9" s="8">
-        <v>0.1785</v>
+        <v>0.06800000000000002</v>
       </c>
       <c r="D9" s="8">
-        <v>0.05354999999999999</v>
+        <v>0.02380000000000001</v>
       </c>
       <c r="E9" s="8">
-        <v>0.6782999999999999</v>
+        <v>0.26180000000000003</v>
       </c>
       <c r="I9" s="6">
         <v>0.75</v>
       </c>
       <c r="J9" s="8">
-        <v>0.7200536319999247</v>
+        <v>2.8269115311078</v>
       </c>
     </row>
     <row r="10">
@@ -3912,22 +3912,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>0.525</v>
+        <v>0.20000000000000004</v>
       </c>
       <c r="C10" s="8">
-        <v>0.21000000000000002</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="D10" s="8">
-        <v>0.063</v>
+        <v>0.028000000000000008</v>
       </c>
       <c r="E10" s="8">
-        <v>0.798</v>
+        <v>0.30800000000000005</v>
       </c>
       <c r="I10" s="6">
         <v>1</v>
       </c>
       <c r="J10" s="8">
-        <v>0.8425085348368556</v>
+        <v>2.9097843218235995</v>
       </c>
     </row>
     <row r="12">
@@ -3978,34 +3978,34 @@
         <v>0</v>
       </c>
       <c r="B14" s="8">
-        <v>2.1</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="C14" s="8">
-        <v>0.8400000000000001</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="D14" s="8">
-        <v>0.25199999999999995</v>
+        <v>0.11200000000000003</v>
       </c>
       <c r="E14" s="8">
-        <v>3.1919999999999997</v>
+        <v>1.2320000000000002</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>0.9576</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="K14" s="13">
-        <v>61.61870674843213</v>
+        <v>30.89893203642754</v>
       </c>
       <c r="L14" s="13">
-        <v>22.27552619310539</v>
+        <v>9.153598393129393</v>
       </c>
       <c r="M14" s="13">
-        <v>7.28129928028104</v>
+        <v>3.3041789424606893</v>
       </c>
       <c r="N14" s="18">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -4013,34 +4013,34 @@
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>2.8875</v>
+        <v>1.1</v>
       </c>
       <c r="C15" s="9">
-        <v>1.155</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="D15" s="9">
-        <v>0.34650000000000003</v>
+        <v>0.15400000000000003</v>
       </c>
       <c r="E15" s="9">
-        <v>4.389</v>
+        <v>1.6940000000000002</v>
       </c>
       <c r="I15" s="7">
         <v>0.25</v>
       </c>
       <c r="J15" s="9">
-        <v>1.3167</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="K15" s="14">
-        <v>73.19816953846153</v>
+        <v>39.84225557590899</v>
       </c>
       <c r="L15" s="14">
-        <v>29.284118071272868</v>
+        <v>12.365900492062675</v>
       </c>
       <c r="M15" s="14">
-        <v>9.872964018737374</v>
+        <v>4.514902710215763</v>
       </c>
       <c r="N15" s="19">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -4048,34 +4048,34 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>3.675</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="C16" s="8">
-        <v>1.47</v>
+        <v>0.56</v>
       </c>
       <c r="D16" s="8">
-        <v>0.441</v>
+        <v>0.19600000000000004</v>
       </c>
       <c r="E16" s="8">
-        <v>5.586</v>
+        <v>2.156</v>
       </c>
       <c r="I16" s="6">
         <v>0.5</v>
       </c>
       <c r="J16" s="8">
-        <v>1.6758</v>
+        <v>0.6468</v>
       </c>
       <c r="K16" s="13">
-        <v>81.28416071389915</v>
+        <v>47.62810010256234</v>
       </c>
       <c r="L16" s="13">
-        <v>35.66072934270438</v>
+        <v>15.464616531534126</v>
       </c>
       <c r="M16" s="13">
-        <v>12.392186778774894</v>
+        <v>5.710467063367641</v>
       </c>
       <c r="N16" s="18">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -4083,34 +4083,34 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>4.4624999999999995</v>
+        <v>1.7000000000000004</v>
       </c>
       <c r="C17" s="8">
-        <v>1.785</v>
+        <v>0.6800000000000002</v>
       </c>
       <c r="D17" s="8">
-        <v>0.5355</v>
+        <v>0.2380000000000001</v>
       </c>
       <c r="E17" s="8">
-        <v>6.7829999999999995</v>
+        <v>2.6180000000000003</v>
       </c>
       <c r="I17" s="6">
         <v>0.75</v>
       </c>
       <c r="J17" s="8">
-        <v>2.0348999999999995</v>
+        <v>0.7854000000000001</v>
       </c>
       <c r="K17" s="13">
-        <v>86.93064487943003</v>
+        <v>54.40627096103638</v>
       </c>
       <c r="L17" s="13">
-        <v>41.46234713038173</v>
+        <v>18.45376288127074</v>
       </c>
       <c r="M17" s="13">
-        <v>14.840992452023826</v>
+        <v>6.891061812224219</v>
       </c>
       <c r="N17" s="18">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -4118,34 +4118,34 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>5.25</v>
+        <v>2.0000000000000004</v>
       </c>
       <c r="C18" s="8">
-        <v>2.1</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="D18" s="8">
-        <v>0.63</v>
+        <v>0.2800000000000001</v>
       </c>
       <c r="E18" s="8">
-        <v>7.98</v>
+        <v>3.0800000000000005</v>
       </c>
       <c r="I18" s="6">
         <v>1</v>
       </c>
       <c r="J18" s="8">
-        <v>2.394</v>
+        <v>0.9240000000000002</v>
       </c>
       <c r="K18" s="13">
-        <v>90.87361027969408</v>
+        <v>60.307185117411755</v>
       </c>
       <c r="L18" s="13">
-        <v>46.74081989931028</v>
+        <v>21.337213893344664</v>
       </c>
       <c r="M18" s="13">
-        <v>17.221349330526635</v>
+        <v>8.056874390487534</v>
       </c>
       <c r="N18" s="18">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -4190,28 +4190,28 @@
         <v>0</v>
       </c>
       <c r="B22" s="8">
-        <v>21</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="C22" s="8">
-        <v>8.4</v>
+        <v>3.2000000000000006</v>
       </c>
       <c r="D22" s="8">
-        <v>2.5199999999999996</v>
+        <v>1.1200000000000003</v>
       </c>
       <c r="E22" s="8">
-        <v>31.919999999999998</v>
+        <v>12.320000000000002</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
       </c>
       <c r="J22" s="8">
-        <v>0.63</v>
+        <v>0.24000000000000005</v>
       </c>
       <c r="K22" s="8">
-        <v>0.252</v>
+        <v>0.09600000000000003</v>
       </c>
       <c r="L22" s="8">
-        <v>0.07559999999999999</v>
+        <v>0.03360000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -4219,28 +4219,28 @@
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>28.875</v>
+        <v>11.000000000000002</v>
       </c>
       <c r="C23" s="9">
-        <v>11.55</v>
+        <v>4.400000000000001</v>
       </c>
       <c r="D23" s="9">
-        <v>3.465</v>
+        <v>1.5400000000000005</v>
       </c>
       <c r="E23" s="9">
-        <v>43.89</v>
+        <v>16.94</v>
       </c>
       <c r="I23" s="6">
         <v>0.25</v>
       </c>
       <c r="J23" s="8">
-        <v>0.86625</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="K23" s="8">
-        <v>0.34650000000000003</v>
+        <v>0.13200000000000003</v>
       </c>
       <c r="L23" s="8">
-        <v>0.10395</v>
+        <v>0.04620000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4248,28 +4248,28 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>36.75</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="C24" s="8">
-        <v>14.7</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D24" s="8">
-        <v>4.41</v>
+        <v>1.9600000000000002</v>
       </c>
       <c r="E24" s="8">
-        <v>55.86</v>
+        <v>21.560000000000002</v>
       </c>
       <c r="I24" s="6">
         <v>0.5</v>
       </c>
       <c r="J24" s="8">
-        <v>1.1025</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="K24" s="8">
-        <v>0.44099999999999995</v>
+        <v>0.16800000000000004</v>
       </c>
       <c r="L24" s="8">
-        <v>0.1323</v>
+        <v>0.058800000000000005</v>
       </c>
     </row>
     <row r="25">
@@ -4277,28 +4277,28 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>44.625</v>
+        <v>17.000000000000004</v>
       </c>
       <c r="C25" s="8">
-        <v>17.849999999999998</v>
+        <v>6.800000000000002</v>
       </c>
       <c r="D25" s="8">
-        <v>5.3549999999999995</v>
+        <v>2.380000000000001</v>
       </c>
       <c r="E25" s="8">
-        <v>67.82999999999998</v>
+        <v>26.180000000000003</v>
       </c>
       <c r="I25" s="6">
         <v>0.75</v>
       </c>
       <c r="J25" s="8">
-        <v>1.3387499999999999</v>
+        <v>0.5100000000000001</v>
       </c>
       <c r="K25" s="8">
-        <v>0.5355</v>
+        <v>0.20400000000000007</v>
       </c>
       <c r="L25" s="8">
-        <v>0.16065</v>
+        <v>0.07140000000000002</v>
       </c>
     </row>
     <row r="26">
@@ -4306,28 +4306,28 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>52.5</v>
+        <v>20.000000000000004</v>
       </c>
       <c r="C26" s="8">
-        <v>21.000000000000004</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="D26" s="8">
-        <v>6.3</v>
+        <v>2.8000000000000007</v>
       </c>
       <c r="E26" s="8">
-        <v>79.80000000000001</v>
+        <v>30.800000000000004</v>
       </c>
       <c r="I26" s="6">
         <v>1</v>
       </c>
       <c r="J26" s="8">
-        <v>1.5750000000000002</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K26" s="8">
-        <v>0.6300000000000001</v>
+        <v>0.24000000000000005</v>
       </c>
       <c r="L26" s="8">
-        <v>0.189</v>
+        <v>0.08400000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -4404,22 +4404,22 @@
         <v>0</v>
       </c>
       <c r="B6" s="8">
-        <v>0.33</v>
+        <v>0.11000000000000001</v>
       </c>
       <c r="C6" s="8">
-        <v>0.132</v>
+        <v>0.04400000000000001</v>
       </c>
       <c r="D6" s="8">
-        <v>0.0396</v>
+        <v>0.015400000000000004</v>
       </c>
       <c r="E6" s="8">
-        <v>0.5016</v>
+        <v>0.16940000000000002</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="8">
-        <v>0.5380969514687323</v>
+        <v>3.047346131064346</v>
       </c>
     </row>
     <row r="7">
@@ -4427,22 +4427,22 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="9">
-        <v>0.5775</v>
+        <v>0.19250000000000003</v>
       </c>
       <c r="C7" s="9">
-        <v>0.231</v>
+        <v>0.07700000000000001</v>
       </c>
       <c r="D7" s="9">
-        <v>0.0693</v>
+        <v>0.02695000000000001</v>
       </c>
       <c r="E7" s="9">
-        <v>0.8778</v>
+        <v>0.2964500000000001</v>
       </c>
       <c r="I7" s="6">
         <v>0.25</v>
       </c>
       <c r="J7" s="8">
-        <v>0.9412098500198062</v>
+        <v>4.373741398705968</v>
       </c>
     </row>
     <row r="8">
@@ -4450,22 +4450,22 @@
         <v>0.5</v>
       </c>
       <c r="B8" s="8">
-        <v>0.8250000000000001</v>
+        <v>0.275</v>
       </c>
       <c r="C8" s="8">
-        <v>0.33000000000000007</v>
+        <v>0.11000000000000001</v>
       </c>
       <c r="D8" s="8">
-        <v>0.099</v>
+        <v>0.038500000000000006</v>
       </c>
       <c r="E8" s="8">
-        <v>1.2540000000000002</v>
+        <v>0.4235</v>
       </c>
       <c r="I8" s="6">
         <v>0.5</v>
       </c>
       <c r="J8" s="8">
-        <v>1.3420737132209009</v>
+        <v>4.847886679313517</v>
       </c>
     </row>
     <row r="9">
@@ -4473,22 +4473,22 @@
         <v>0.75</v>
       </c>
       <c r="B9" s="8">
-        <v>1.0725</v>
+        <v>0.35750000000000004</v>
       </c>
       <c r="C9" s="8">
-        <v>0.42900000000000005</v>
+        <v>0.14300000000000002</v>
       </c>
       <c r="D9" s="8">
-        <v>0.1287</v>
+        <v>0.05005000000000001</v>
       </c>
       <c r="E9" s="8">
-        <v>1.6302</v>
+        <v>0.5505500000000001</v>
       </c>
       <c r="I9" s="6">
         <v>0.75</v>
       </c>
       <c r="J9" s="8">
-        <v>1.737016465278785</v>
+        <v>4.969439390356537</v>
       </c>
     </row>
     <row r="10">
@@ -4496,22 +4496,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="8">
-        <v>1.32</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="C10" s="8">
-        <v>0.528</v>
+        <v>0.17600000000000005</v>
       </c>
       <c r="D10" s="8">
-        <v>0.1584</v>
+        <v>0.061600000000000016</v>
       </c>
       <c r="E10" s="8">
-        <v>2.0064</v>
+        <v>0.6776000000000001</v>
       </c>
       <c r="I10" s="6">
         <v>1</v>
       </c>
       <c r="J10" s="8">
-        <v>2.1208613717224276</v>
+        <v>4.994624663556874</v>
       </c>
     </row>
     <row r="12">
@@ -4562,34 +4562,34 @@
         <v>0</v>
       </c>
       <c r="B14" s="8">
-        <v>3.3000000000000003</v>
+        <v>1.1</v>
       </c>
       <c r="C14" s="8">
-        <v>1.32</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="D14" s="8">
-        <v>0.396</v>
+        <v>0.15400000000000003</v>
       </c>
       <c r="E14" s="8">
-        <v>5.016</v>
+        <v>1.6940000000000002</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
       </c>
       <c r="J14" s="8">
-        <v>1.5048000000000001</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="K14" s="13">
-        <v>77.79382982686424</v>
+        <v>39.84225557590899</v>
       </c>
       <c r="L14" s="13">
-        <v>32.69933040626136</v>
+        <v>12.365900492062675</v>
       </c>
       <c r="M14" s="13">
-        <v>11.201461992055773</v>
+        <v>4.514902710215763</v>
       </c>
       <c r="N14" s="18">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -4597,34 +4597,34 @@
         <v>0.25</v>
       </c>
       <c r="B15" s="9">
-        <v>5.775</v>
+        <v>1.9250000000000003</v>
       </c>
       <c r="C15" s="9">
-        <v>2.31</v>
+        <v>0.7700000000000001</v>
       </c>
       <c r="D15" s="9">
-        <v>0.6930000000000001</v>
+        <v>0.2695000000000001</v>
       </c>
       <c r="E15" s="9">
-        <v>8.778</v>
+        <v>2.964500000000001</v>
       </c>
       <c r="I15" s="7">
         <v>0.25</v>
       </c>
       <c r="J15" s="9">
-        <v>2.6334</v>
+        <v>0.8893500000000003</v>
       </c>
       <c r="K15" s="14">
-        <v>92.8166188391095</v>
+        <v>58.907723423853874</v>
       </c>
       <c r="L15" s="14">
-        <v>49.99264043042324</v>
+        <v>20.62605339647573</v>
       </c>
       <c r="M15" s="14">
-        <v>18.771173852321922</v>
+        <v>7.766796912647744</v>
       </c>
       <c r="N15" s="19">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -4632,34 +4632,34 @@
         <v>0.5</v>
       </c>
       <c r="B16" s="8">
-        <v>8.25</v>
+        <v>2.75</v>
       </c>
       <c r="C16" s="8">
-        <v>3.3000000000000007</v>
+        <v>1.1</v>
       </c>
       <c r="D16" s="8">
-        <v>0.99</v>
+        <v>0.38500000000000006</v>
       </c>
       <c r="E16" s="8">
-        <v>12.540000000000003</v>
+        <v>4.234999999999999</v>
       </c>
       <c r="I16" s="6">
         <v>0.5</v>
       </c>
       <c r="J16" s="8">
-        <v>3.7620000000000005</v>
+        <v>1.2705</v>
       </c>
       <c r="K16" s="13">
-        <v>97.67627805694015</v>
+        <v>71.93087589344066</v>
       </c>
       <c r="L16" s="13">
-        <v>62.84233089779544</v>
+        <v>28.107626656807383</v>
       </c>
       <c r="M16" s="13">
-        <v>25.695598763806014</v>
+        <v>10.90794277629219</v>
       </c>
       <c r="N16" s="18">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -4667,34 +4667,34 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="8">
-        <v>10.725</v>
+        <v>3.575</v>
       </c>
       <c r="C17" s="8">
-        <v>4.290000000000001</v>
+        <v>1.4300000000000002</v>
       </c>
       <c r="D17" s="8">
-        <v>1.2870000000000001</v>
+        <v>0.5005000000000002</v>
       </c>
       <c r="E17" s="8">
-        <v>16.302</v>
+        <v>5.505500000000001</v>
       </c>
       <c r="I17" s="6">
         <v>0.75</v>
       </c>
       <c r="J17" s="8">
-        <v>4.8906</v>
+        <v>1.6516500000000003</v>
       </c>
       <c r="K17" s="13">
-        <v>99.24830890249065</v>
+        <v>80.82667124442582</v>
       </c>
       <c r="L17" s="13">
-        <v>72.39021646028064</v>
+        <v>34.88400708189675</v>
       </c>
       <c r="M17" s="13">
-        <v>32.029744797350766</v>
+        <v>13.942112008892538</v>
       </c>
       <c r="N17" s="18">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -4702,34 +4702,34 @@
         <v>1</v>
       </c>
       <c r="B18" s="8">
-        <v>13.200000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="C18" s="8">
-        <v>5.28</v>
+        <v>1.7600000000000005</v>
       </c>
       <c r="D18" s="8">
-        <v>1.584</v>
+        <v>0.6160000000000001</v>
       </c>
       <c r="E18" s="8">
-        <v>20.064</v>
+        <v>6.776000000000001</v>
       </c>
       <c r="I18" s="6">
         <v>1</v>
       </c>
       <c r="J18" s="8">
-        <v>6.0192000000000005</v>
+        <v>2.0328000000000004</v>
       </c>
       <c r="K18" s="13">
-        <v>99.75683858915977</v>
+        <v>86.90317039556565</v>
       </c>
       <c r="L18" s="13">
-        <v>79.48471565820229</v>
+        <v>41.02166423871496</v>
       </c>
       <c r="M18" s="13">
-        <v>37.8239308109401</v>
+        <v>16.87294786679101</v>
       </c>
       <c r="N18" s="18">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -4774,28 +4774,28 @@
         <v>0</v>
       </c>
       <c r="B22" s="8">
-        <v>33</v>
+        <v>11.000000000000002</v>
       </c>
       <c r="C22" s="8">
-        <v>13.200000000000001</v>
+        <v>4.400000000000001</v>
       </c>
       <c r="D22" s="8">
-        <v>3.9600000000000004</v>
+        <v>1.5400000000000005</v>
       </c>
       <c r="E22" s="8">
-        <v>50.160000000000004</v>
+        <v>16.94</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
       </c>
       <c r="J22" s="8">
-        <v>0.99</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="K22" s="8">
-        <v>0.396</v>
+        <v>0.13200000000000003</v>
       </c>
       <c r="L22" s="8">
-        <v>0.11880000000000002</v>
+        <v>0.04620000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -4803,28 +4803,28 @@
         <v>0.25</v>
       </c>
       <c r="B23" s="9">
-        <v>57.75</v>
+        <v>19.250000000000004</v>
       </c>
       <c r="C23" s="9">
-        <v>23.1</v>
+        <v>7.700000000000001</v>
       </c>
       <c r="D23" s="9">
-        <v>6.93</v>
+        <v>2.6950000000000007</v>
       </c>
       <c r="E23" s="9">
-        <v>87.78</v>
+        <v>29.64500000000001</v>
       </c>
       <c r="I23" s="6">
         <v>0.25</v>
       </c>
       <c r="J23" s="8">
-        <v>1.7325</v>
+        <v>0.5775000000000001</v>
       </c>
       <c r="K23" s="8">
-        <v>0.6930000000000001</v>
+        <v>0.23100000000000004</v>
       </c>
       <c r="L23" s="8">
-        <v>0.2079</v>
+        <v>0.08085000000000003</v>
       </c>
     </row>
     <row r="24">
@@ -4832,28 +4832,28 @@
         <v>0.5</v>
       </c>
       <c r="B24" s="8">
-        <v>82.5</v>
+        <v>27.500000000000004</v>
       </c>
       <c r="C24" s="8">
-        <v>33.00000000000001</v>
+        <v>11.000000000000002</v>
       </c>
       <c r="D24" s="8">
-        <v>9.9</v>
+        <v>3.8500000000000005</v>
       </c>
       <c r="E24" s="8">
-        <v>125.40000000000002</v>
+        <v>42.35</v>
       </c>
       <c r="I24" s="6">
         <v>0.5</v>
       </c>
       <c r="J24" s="8">
-        <v>2.475</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="K24" s="8">
-        <v>0.9900000000000002</v>
+        <v>0.33000000000000007</v>
       </c>
       <c r="L24" s="8">
-        <v>0.29700000000000004</v>
+        <v>0.11550000000000002</v>
       </c>
     </row>
     <row r="25">
@@ -4861,28 +4861,28 @@
         <v>0.75</v>
       </c>
       <c r="B25" s="8">
-        <v>107.25</v>
+        <v>35.75000000000001</v>
       </c>
       <c r="C25" s="8">
-        <v>42.900000000000006</v>
+        <v>14.3</v>
       </c>
       <c r="D25" s="8">
-        <v>12.870000000000001</v>
+        <v>5.005000000000001</v>
       </c>
       <c r="E25" s="8">
-        <v>163.02</v>
+        <v>55.05500000000001</v>
       </c>
       <c r="I25" s="6">
         <v>0.75</v>
       </c>
       <c r="J25" s="8">
-        <v>3.2175000000000002</v>
+        <v>1.0725000000000002</v>
       </c>
       <c r="K25" s="8">
-        <v>1.2870000000000001</v>
+        <v>0.42900000000000005</v>
       </c>
       <c r="L25" s="8">
-        <v>0.3861</v>
+        <v>0.15015000000000003</v>
       </c>
     </row>
     <row r="26">
@@ -4890,28 +4890,28 @@
         <v>1</v>
       </c>
       <c r="B26" s="8">
-        <v>132</v>
+        <v>44.00000000000001</v>
       </c>
       <c r="C26" s="8">
-        <v>52.800000000000004</v>
+        <v>17.600000000000005</v>
       </c>
       <c r="D26" s="8">
-        <v>15.840000000000002</v>
+        <v>6.160000000000002</v>
       </c>
       <c r="E26" s="8">
-        <v>200.64000000000001</v>
+        <v>67.76</v>
       </c>
       <c r="I26" s="6">
         <v>1</v>
       </c>
       <c r="J26" s="8">
-        <v>3.96</v>
+        <v>1.3200000000000003</v>
       </c>
       <c r="K26" s="8">
-        <v>1.584</v>
+        <v>0.5280000000000001</v>
       </c>
       <c r="L26" s="8">
-        <v>0.47520000000000007</v>
+        <v>0.18480000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -4961,16 +4961,16 @@
         <v>0</v>
       </c>
       <c r="B49" s="8">
-        <v>0.378</v>
+        <v>0.126</v>
       </c>
       <c r="C49" s="8">
-        <v>0.6839999999999999</v>
+        <v>0.25410000000000005</v>
       </c>
       <c r="D49" s="8">
-        <v>0.9576</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="E49" s="8">
-        <v>1.5048000000000001</v>
+        <v>0.5082000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4978,16 +4978,16 @@
         <v>0.25</v>
       </c>
       <c r="B50" s="8">
-        <v>0.4724999999999999</v>
+        <v>0.1575</v>
       </c>
       <c r="C50" s="8">
-        <v>0.8550000000000001</v>
+        <v>0.317625</v>
       </c>
       <c r="D50" s="8">
-        <v>1.3167</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="E50" s="8">
-        <v>2.6334</v>
+        <v>0.8893500000000003</v>
       </c>
     </row>
     <row r="51">
@@ -4995,16 +4995,16 @@
         <v>0.5</v>
       </c>
       <c r="B51" s="8">
-        <v>0.567</v>
+        <v>0.189</v>
       </c>
       <c r="C51" s="8">
-        <v>1.0259999999999998</v>
+        <v>0.3811500000000001</v>
       </c>
       <c r="D51" s="8">
-        <v>1.6758</v>
+        <v>0.6468</v>
       </c>
       <c r="E51" s="8">
-        <v>3.7620000000000005</v>
+        <v>1.2705</v>
       </c>
     </row>
     <row r="52">
@@ -5012,16 +5012,16 @@
         <v>0.75</v>
       </c>
       <c r="B52" s="8">
-        <v>0.6615</v>
+        <v>0.22049999999999997</v>
       </c>
       <c r="C52" s="8">
-        <v>1.197</v>
+        <v>0.44467500000000015</v>
       </c>
       <c r="D52" s="8">
-        <v>2.0348999999999995</v>
+        <v>0.7854000000000001</v>
       </c>
       <c r="E52" s="8">
-        <v>4.8906</v>
+        <v>1.6516500000000003</v>
       </c>
     </row>
     <row r="53">
@@ -5029,16 +5029,16 @@
         <v>1</v>
       </c>
       <c r="B53" s="8">
-        <v>0.756</v>
+        <v>0.252</v>
       </c>
       <c r="C53" s="8">
-        <v>1.3679999999999999</v>
+        <v>0.5082000000000001</v>
       </c>
       <c r="D53" s="8">
-        <v>2.394</v>
+        <v>0.9240000000000002</v>
       </c>
       <c r="E53" s="8">
-        <v>6.0192000000000005</v>
+        <v>2.0328000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -5114,7 +5114,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="8">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>15</v>
@@ -5140,13 +5140,13 @@
         <v>63</v>
       </c>
       <c r="B7" s="33">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F7" s="8">
         <v>2</v>
@@ -5172,7 +5172,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="8">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F8" s="8">
         <v>2.5</v>
@@ -5218,7 +5218,7 @@
         <v>69</v>
       </c>
       <c r="B10" s="8">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="11">
